--- a/Part4/All Ficnal data.xlsx
+++ b/Part4/All Ficnal data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ehsan\Documents\Disertation\Word - June to\stock-market\Stocks5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ehsan\Documents\Disertation\Word - June to\stock-market\Part4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59D4AAA5-9AE4-4AF7-94A7-6DD9C27A4363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{379D5285-98EB-4A8B-9414-839EC7CC943F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Marks &amp; Spencer" sheetId="3" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="18">
   <si>
     <t>Year</t>
   </si>
@@ -78,6 +78,9 @@
   </si>
   <si>
     <t>CEO Change</t>
+  </si>
+  <si>
+    <t>Avg_FSTE_Price</t>
   </si>
 </sst>
 </file>
@@ -162,7 +165,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -183,6 +186,17 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -230,11 +244,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -543,7 +557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6295256-9C2A-4094-9ED8-C96318F4096C}">
-  <dimension ref="A1:Q37"/>
+  <dimension ref="A1:R37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
@@ -562,10 +576,10 @@
     <col min="15" max="15" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -614,11 +628,14 @@
       <c r="P1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="14" t="s">
+      <c r="Q1" s="5" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:17">
+      <c r="R1" s="13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2" s="2">
         <v>2015</v>
       </c>
@@ -659,7 +676,7 @@
         <v>18</v>
       </c>
       <c r="M2" s="2">
-        <f>O2-P2</f>
+        <f t="shared" ref="M2:M13" si="2">O2-P2</f>
         <v>628.9</v>
       </c>
       <c r="N2" s="2">
@@ -674,8 +691,11 @@
       <c r="Q2" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:17">
+      <c r="R2" s="2">
+        <v>6641.77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3" s="2">
         <v>2016</v>
       </c>
@@ -709,14 +729,14 @@
         <v>196000000</v>
       </c>
       <c r="K3" s="2">
-        <f t="shared" ref="K3" si="2">ROUND(J3/I3*100,2)</f>
+        <f t="shared" ref="K3" si="3">ROUND(J3/I3*100,2)</f>
         <v>5.69</v>
       </c>
       <c r="L3" s="2">
         <v>18.7</v>
       </c>
       <c r="M3" s="2">
-        <f>O3-P3</f>
+        <f t="shared" si="2"/>
         <v>635.9</v>
       </c>
       <c r="N3" s="2">
@@ -731,8 +751,11 @@
       <c r="Q3" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:17">
+      <c r="R3" s="2">
+        <v>6335.38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" s="2">
         <v>2017</v>
       </c>
@@ -743,7 +766,7 @@
         <v>253200000</v>
       </c>
       <c r="D4" s="2">
-        <f>ROUND(C4/B4*100,2)</f>
+        <f t="shared" ref="D4:D12" si="4">ROUND(C4/B4*100,2)</f>
         <v>2.38</v>
       </c>
       <c r="E4" s="4">
@@ -753,7 +776,7 @@
         <v>115700000</v>
       </c>
       <c r="G4" s="2">
-        <f>ROUND(F4/B4*100,2)</f>
+        <f t="shared" ref="G4:G22" si="5">ROUND(F4/B4*100,2)</f>
         <v>1.0900000000000001</v>
       </c>
       <c r="H4" s="2">
@@ -766,14 +789,14 @@
         <v>406200000</v>
       </c>
       <c r="K4" s="2">
-        <f>ROUND(J4/I4*100,2)</f>
+        <f t="shared" ref="K4:K12" si="6">ROUND(J4/I4*100,2)</f>
         <v>12.89</v>
       </c>
       <c r="L4" s="2">
         <v>18.7</v>
       </c>
       <c r="M4" s="2">
-        <f>O4-P4</f>
+        <f t="shared" si="2"/>
         <v>695.7</v>
       </c>
       <c r="N4" s="2">
@@ -788,8 +811,11 @@
       <c r="Q4" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:17">
+      <c r="R4" s="2">
+        <v>6842.83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5" s="2">
         <v>2018</v>
       </c>
@@ -800,7 +826,7 @@
         <v>156500000</v>
       </c>
       <c r="D5" s="2">
-        <f>ROUND(C5/B5*100,2)</f>
+        <f t="shared" si="4"/>
         <v>1.46</v>
       </c>
       <c r="E5" s="4">
@@ -810,7 +836,7 @@
         <v>29100000</v>
       </c>
       <c r="G5" s="2">
-        <f>ROUND(F5/B5*100,2)</f>
+        <f t="shared" si="5"/>
         <v>0.27</v>
       </c>
       <c r="H5" s="2">
@@ -823,30 +849,33 @@
         <v>171000000</v>
       </c>
       <c r="K5" s="2">
-        <f>ROUND(J5/I5*100,2)</f>
+        <f t="shared" si="6"/>
         <v>5.79</v>
       </c>
       <c r="L5" s="2">
         <v>18.7</v>
       </c>
       <c r="M5" s="2">
-        <f>O5-P5</f>
+        <f t="shared" si="2"/>
         <v>533.5</v>
       </c>
       <c r="N5" s="2">
         <v>310.35000000000002</v>
       </c>
-      <c r="O5" s="13">
+      <c r="O5" s="2">
         <v>849.8</v>
       </c>
-      <c r="P5" s="13">
+      <c r="P5" s="2">
         <v>316.3</v>
       </c>
       <c r="Q5" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:17">
+      <c r="R5" s="2">
+        <v>7428.21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6" s="2">
         <v>2019</v>
       </c>
@@ -857,7 +886,7 @@
         <v>298100000</v>
       </c>
       <c r="D6" s="2">
-        <f>ROUND(C6/B6*100,2)</f>
+        <f t="shared" si="4"/>
         <v>2.87</v>
       </c>
       <c r="E6" s="4">
@@ -867,7 +896,7 @@
         <v>45300000</v>
       </c>
       <c r="G6" s="2">
-        <f>ROUND(F6/B6*100,2)</f>
+        <f t="shared" si="5"/>
         <v>0.44</v>
       </c>
       <c r="H6" s="2">
@@ -880,30 +909,33 @@
         <v>213100000</v>
       </c>
       <c r="K6" s="2">
-        <f>ROUND(J6/I6*100,2)</f>
+        <f t="shared" si="6"/>
         <v>8.6300000000000008</v>
       </c>
       <c r="L6" s="2">
         <v>18.7</v>
       </c>
       <c r="M6" s="2">
-        <f>O6-P6</f>
+        <f t="shared" si="2"/>
         <v>856.7</v>
       </c>
       <c r="N6" s="2">
         <v>277.88</v>
       </c>
-      <c r="O6" s="13">
+      <c r="O6" s="2">
         <v>1244.7</v>
       </c>
-      <c r="P6" s="13">
+      <c r="P6" s="2">
         <v>388</v>
       </c>
       <c r="Q6" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:17">
+      <c r="R6" s="14">
+        <v>7276.89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
       <c r="A7" s="2">
         <v>2020</v>
       </c>
@@ -914,7 +946,7 @@
         <v>254800000</v>
       </c>
       <c r="D7" s="2">
-        <f>ROUND(C7/B7*100,2)</f>
+        <f t="shared" si="4"/>
         <v>2.5</v>
       </c>
       <c r="E7" s="4">
@@ -924,7 +956,7 @@
         <v>27400000</v>
       </c>
       <c r="G7" s="2">
-        <f>ROUND(F7/B7*100,2)</f>
+        <f t="shared" si="5"/>
         <v>0.27</v>
       </c>
       <c r="H7" s="2">
@@ -937,30 +969,33 @@
         <v>164100000</v>
       </c>
       <c r="K7" s="2">
-        <f>ROUND(J7/I7*100,2)</f>
+        <f t="shared" si="6"/>
         <v>4.42</v>
       </c>
       <c r="L7" s="2">
         <v>10.7</v>
       </c>
       <c r="M7" s="2">
-        <f>O7-P7</f>
+        <f t="shared" si="2"/>
         <v>207.39999999999998</v>
       </c>
       <c r="N7" s="2">
         <v>195.53</v>
       </c>
-      <c r="O7" s="13">
+      <c r="O7" s="2">
         <v>973.1</v>
       </c>
-      <c r="P7" s="13">
+      <c r="P7" s="2">
         <v>765.7</v>
       </c>
       <c r="Q7" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:17">
+      <c r="R7" s="14">
+        <v>7341.89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
       <c r="A8" s="2">
         <v>2021</v>
       </c>
@@ -971,7 +1006,7 @@
         <v>-30700000</v>
       </c>
       <c r="D8" s="2">
-        <f>ROUND(C8/B8*100,2)</f>
+        <f t="shared" si="4"/>
         <v>-0.34</v>
       </c>
       <c r="E8" s="4">
@@ -981,7 +1016,7 @@
         <v>-201200000</v>
       </c>
       <c r="G8" s="2">
-        <f>ROUND(F8/B8*100,2)</f>
+        <f t="shared" si="5"/>
         <v>-2.2000000000000002</v>
       </c>
       <c r="H8" s="2">
@@ -994,30 +1029,33 @@
         <v>669700000</v>
       </c>
       <c r="K8" s="2">
-        <f>ROUND(J8/I8*100,2)</f>
+        <f t="shared" si="6"/>
         <v>29.3</v>
       </c>
       <c r="L8" s="2">
         <v>0</v>
       </c>
       <c r="M8" s="2">
-        <f>O8-P8</f>
+        <f t="shared" si="2"/>
         <v>678.3</v>
       </c>
       <c r="N8" s="2">
         <v>110.17</v>
       </c>
-      <c r="O8" s="13">
+      <c r="O8" s="2">
         <v>870.9</v>
       </c>
-      <c r="P8" s="13">
+      <c r="P8" s="2">
         <v>192.6</v>
       </c>
       <c r="Q8" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:17">
+      <c r="R8" s="14">
+        <v>6122.66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
       <c r="A9" s="2">
         <v>2022</v>
       </c>
@@ -1028,7 +1066,7 @@
         <v>572200000</v>
       </c>
       <c r="D9" s="2">
-        <f>ROUND(C9/B9*100,2)</f>
+        <f t="shared" si="4"/>
         <v>5.26</v>
       </c>
       <c r="E9" s="4">
@@ -1038,7 +1076,7 @@
         <v>309000000</v>
       </c>
       <c r="G9" s="2">
-        <f>ROUND(F9/B9*100,2)</f>
+        <f t="shared" si="5"/>
         <v>2.84</v>
       </c>
       <c r="H9" s="2">
@@ -1051,30 +1089,33 @@
         <v>1197900000</v>
       </c>
       <c r="K9" s="2">
-        <f>ROUND(J9/I9*100,2)</f>
+        <f t="shared" si="6"/>
         <v>41.07</v>
       </c>
       <c r="L9" s="2">
         <v>0</v>
       </c>
       <c r="M9" s="2">
-        <f>O9-P9</f>
+        <f t="shared" si="2"/>
         <v>1132.3</v>
       </c>
       <c r="N9" s="2">
         <v>186.59</v>
       </c>
-      <c r="O9" s="13">
+      <c r="O9" s="2">
         <v>1378</v>
       </c>
-      <c r="P9" s="13">
+      <c r="P9" s="2">
         <v>245.7</v>
       </c>
       <c r="Q9" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:17">
+      <c r="R9" s="14">
+        <v>7159.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
       <c r="A10" s="2">
         <v>2023</v>
       </c>
@@ -1085,7 +1126,7 @@
         <v>515100000</v>
       </c>
       <c r="D10" s="2">
-        <f>ROUND(C10/B10*100,2)</f>
+        <f t="shared" si="4"/>
         <v>4.32</v>
       </c>
       <c r="E10" s="4">
@@ -1095,7 +1136,7 @@
         <v>364500000</v>
       </c>
       <c r="G10" s="2">
-        <f>ROUND(F10/B10*100,2)</f>
+        <f t="shared" si="5"/>
         <v>3.05</v>
       </c>
       <c r="H10" s="2">
@@ -1108,30 +1149,33 @@
         <v>1067900000</v>
       </c>
       <c r="K10" s="2">
-        <f>ROUND(J10/I10*100,2)</f>
+        <f t="shared" si="6"/>
         <v>39.840000000000003</v>
       </c>
       <c r="L10" s="2">
         <v>0</v>
       </c>
       <c r="M10" s="2">
-        <f>O10-P10</f>
+        <f t="shared" si="2"/>
         <v>513.30000000000007</v>
       </c>
       <c r="N10" s="2">
         <v>121.4</v>
       </c>
-      <c r="O10" s="13">
+      <c r="O10" s="2">
         <v>1029.9000000000001</v>
       </c>
-      <c r="P10" s="13">
+      <c r="P10" s="2">
         <v>516.6</v>
       </c>
       <c r="Q10" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:17">
+      <c r="R10" s="14">
+        <v>7283.02</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
       <c r="A11" s="2">
         <v>2024</v>
       </c>
@@ -1142,7 +1186,7 @@
         <v>714200000</v>
       </c>
       <c r="D11" s="2">
-        <f>ROUND(C11/B11*100,2)</f>
+        <f t="shared" si="4"/>
         <v>5.48</v>
       </c>
       <c r="E11" s="4">
@@ -1152,7 +1196,7 @@
         <v>425200000</v>
       </c>
       <c r="G11" s="2">
-        <f>ROUND(F11/B11*100,2)</f>
+        <f t="shared" si="5"/>
         <v>3.26</v>
       </c>
       <c r="H11" s="2">
@@ -1165,30 +1209,33 @@
         <v>1022400000</v>
       </c>
       <c r="K11" s="2">
-        <f>ROUND(J11/I11*100,2)</f>
+        <f t="shared" si="6"/>
         <v>36.130000000000003</v>
       </c>
       <c r="L11" s="2">
         <v>3</v>
       </c>
       <c r="M11" s="2">
-        <f>O11-P11</f>
+        <f t="shared" si="2"/>
         <v>866.2</v>
       </c>
       <c r="N11" s="2">
         <v>227.6</v>
       </c>
-      <c r="O11" s="13">
+      <c r="O11" s="2">
         <v>1301.7</v>
       </c>
-      <c r="P11" s="13">
+      <c r="P11" s="2">
         <v>435.5</v>
       </c>
       <c r="Q11" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:17">
+      <c r="R11" s="14">
+        <v>7508.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
       <c r="A12" s="2">
         <v>2025</v>
       </c>
@@ -1199,7 +1246,7 @@
         <v>624300000</v>
       </c>
       <c r="D12" s="2">
-        <f>ROUND(C12/B12*100,2)</f>
+        <f t="shared" si="4"/>
         <v>4.5199999999999996</v>
       </c>
       <c r="E12" s="4">
@@ -1209,7 +1256,7 @@
         <v>291900000</v>
       </c>
       <c r="G12" s="2">
-        <f>ROUND(F12/B12*100,2)</f>
+        <f t="shared" si="5"/>
         <v>2.11</v>
       </c>
       <c r="H12" s="2">
@@ -1222,30 +1269,33 @@
         <v>864500000</v>
       </c>
       <c r="K12" s="2">
-        <f>ROUND(J12/I12*100,2)</f>
+        <f t="shared" si="6"/>
         <v>29.3</v>
       </c>
       <c r="L12" s="2">
         <v>3.6</v>
       </c>
       <c r="M12" s="2">
-        <f>O12-P12</f>
+        <f t="shared" si="2"/>
         <v>616.9</v>
       </c>
       <c r="N12" s="2">
         <v>355.93</v>
       </c>
-      <c r="O12" s="13">
+      <c r="O12" s="2">
         <v>1313</v>
       </c>
-      <c r="P12" s="13">
+      <c r="P12" s="2">
         <v>696.1</v>
       </c>
       <c r="Q12" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:17">
+      <c r="R12" s="14">
+        <v>8231.6200000000008</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
       <c r="A13" s="2">
         <v>2015.5</v>
       </c>
@@ -1256,7 +1306,7 @@
         <v>339000000</v>
       </c>
       <c r="D13" s="2">
-        <f t="shared" ref="D13:D22" si="3">ROUND(C13/B13*100,2)</f>
+        <f t="shared" ref="D13:D14" si="7">ROUND(C13/B13*100,2)</f>
         <v>6.85</v>
       </c>
       <c r="E13" s="4">
@@ -1266,7 +1316,7 @@
         <v>170700000</v>
       </c>
       <c r="G13" s="2">
-        <f>ROUND(F13/B13*100,2)</f>
+        <f t="shared" si="5"/>
         <v>3.45</v>
       </c>
       <c r="H13" s="2">
@@ -1279,14 +1329,14 @@
         <v>167200000</v>
       </c>
       <c r="K13" s="2">
-        <f t="shared" ref="K13:K22" si="4">ROUND(J13/I13*100,2)</f>
+        <f t="shared" ref="K13:K14" si="8">ROUND(J13/I13*100,2)</f>
         <v>5.46</v>
       </c>
       <c r="L13" s="2">
         <v>6.8</v>
       </c>
       <c r="M13" s="2">
-        <f>O13-P13</f>
+        <f t="shared" si="2"/>
         <v>313.69999999999993</v>
       </c>
       <c r="N13" s="2">
@@ -1301,8 +1351,11 @@
       <c r="Q13" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17">
+      <c r="R13" s="14">
+        <v>6855.45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
       <c r="A14" s="2">
         <v>2016.5</v>
       </c>
@@ -1313,7 +1366,7 @@
         <v>62500000</v>
       </c>
       <c r="D14" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1.25</v>
       </c>
       <c r="E14" s="4">
@@ -1323,7 +1376,7 @@
         <v>15600000</v>
       </c>
       <c r="G14" s="2">
-        <f>ROUND(F14/B14*100,2)</f>
+        <f t="shared" si="5"/>
         <v>0.31</v>
       </c>
       <c r="H14" s="2">
@@ -1336,14 +1389,14 @@
         <v>121200000</v>
       </c>
       <c r="K14" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>3.88</v>
       </c>
       <c r="L14" s="2">
         <v>6.8</v>
       </c>
       <c r="M14" s="2">
-        <f t="shared" ref="M14:M17" si="5">O14-P14</f>
+        <f t="shared" ref="M14" si="9">O14-P14</f>
         <v>219.3</v>
       </c>
       <c r="N14" s="2">
@@ -1358,8 +1411,11 @@
       <c r="Q14" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:17">
+      <c r="R14" s="14">
+        <v>6097.14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
       <c r="A15" s="2">
         <v>2017.5</v>
       </c>
@@ -1370,7 +1426,7 @@
         <v>165300000</v>
       </c>
       <c r="D15" s="2">
-        <f>ROUND(C15/B15*100,2)</f>
+        <f t="shared" ref="D15:D22" si="10">ROUND(C15/B15*100,2)</f>
         <v>3.22</v>
       </c>
       <c r="E15" s="4">
@@ -1380,7 +1436,7 @@
         <v>84600000</v>
       </c>
       <c r="G15" s="2">
-        <f>ROUND(F15/B15*100,2)</f>
+        <f t="shared" si="5"/>
         <v>1.65</v>
       </c>
       <c r="H15" s="2">
@@ -1393,14 +1449,14 @@
         <v>251000000</v>
       </c>
       <c r="K15" s="2">
-        <f>ROUND(J15/I15*100,2)</f>
+        <f t="shared" ref="K15:K22" si="11">ROUND(J15/I15*100,2)</f>
         <v>8.7100000000000009</v>
       </c>
       <c r="L15" s="2">
         <v>6.8</v>
       </c>
       <c r="M15" s="2">
-        <f>O15-P15</f>
+        <f t="shared" ref="M15:M22" si="12">O15-P15</f>
         <v>152.29999999999998</v>
       </c>
       <c r="N15" s="2">
@@ -1415,8 +1471,11 @@
       <c r="Q15" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17">
+      <c r="R15" s="14">
+        <v>7330.76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
       <c r="A16" s="2">
         <v>2018.5</v>
       </c>
@@ -1427,7 +1486,7 @@
         <v>165700000</v>
       </c>
       <c r="D16" s="2">
-        <f>ROUND(C16/B16*100,2)</f>
+        <f t="shared" si="10"/>
         <v>3.31</v>
       </c>
       <c r="E16" s="4">
@@ -1437,7 +1496,7 @@
         <v>89800000</v>
       </c>
       <c r="G16" s="2">
-        <f>ROUND(F16/B16*100,2)</f>
+        <f t="shared" si="5"/>
         <v>1.8</v>
       </c>
       <c r="H16" s="2">
@@ -1450,14 +1509,14 @@
         <v>114000000</v>
       </c>
       <c r="K16" s="2">
-        <f>ROUND(J16/I16*100,2)</f>
+        <f t="shared" si="11"/>
         <v>3.95</v>
       </c>
       <c r="L16" s="2">
         <v>6.8</v>
       </c>
       <c r="M16" s="2">
-        <f>O16-P16</f>
+        <f t="shared" si="12"/>
         <v>278.29999999999995</v>
       </c>
       <c r="N16" s="2">
@@ -1472,8 +1531,11 @@
       <c r="Q16" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:17">
+      <c r="R16" s="14">
+        <v>7450.95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
       <c r="A17" s="2">
         <v>2019.5</v>
       </c>
@@ -1484,7 +1546,7 @@
         <v>252400000</v>
       </c>
       <c r="D17" s="2">
-        <f>ROUND(C17/B17*100,2)</f>
+        <f t="shared" si="10"/>
         <v>5.19</v>
       </c>
       <c r="E17" s="4">
@@ -1494,7 +1556,7 @@
         <v>122400000</v>
       </c>
       <c r="G17" s="2">
-        <f>ROUND(F17/B17*100,2)</f>
+        <f t="shared" si="5"/>
         <v>2.52</v>
       </c>
       <c r="H17" s="2">
@@ -1507,14 +1569,14 @@
         <v>307600000</v>
       </c>
       <c r="K17" s="2">
-        <f>ROUND(J17/I17*100,2)</f>
+        <f t="shared" si="11"/>
         <v>9.8699999999999992</v>
       </c>
       <c r="L17" s="2">
         <v>3.9</v>
       </c>
       <c r="M17" s="2">
-        <f>O17-P17</f>
+        <f t="shared" si="12"/>
         <v>-358.2</v>
       </c>
       <c r="N17" s="2">
@@ -1529,8 +1591,11 @@
       <c r="Q17" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:17">
+      <c r="R17" s="14">
+        <v>7208.45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
       <c r="A18" s="2">
         <v>2020.5</v>
       </c>
@@ -1541,7 +1606,7 @@
         <v>-9400000</v>
       </c>
       <c r="D18" s="2">
-        <f>ROUND(C18/B18*100,2)</f>
+        <f t="shared" si="10"/>
         <v>-0.23</v>
       </c>
       <c r="E18" s="4">
@@ -1551,7 +1616,7 @@
         <v>-71600000</v>
       </c>
       <c r="G18" s="2">
-        <f>ROUND(F18/B18*100,2)</f>
+        <f t="shared" si="5"/>
         <v>-1.75</v>
       </c>
       <c r="H18" s="2">
@@ -1564,14 +1629,14 @@
         <v>222500000</v>
       </c>
       <c r="K18" s="2">
-        <f>ROUND(J18/I18*100,2)</f>
+        <f t="shared" si="11"/>
         <v>8.1999999999999993</v>
       </c>
       <c r="L18" s="2">
         <v>0</v>
       </c>
       <c r="M18" s="2">
-        <f>O18-P18</f>
+        <f t="shared" si="12"/>
         <v>230.5</v>
       </c>
       <c r="N18" s="2">
@@ -1586,8 +1651,11 @@
       <c r="Q18" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:17">
+      <c r="R18" s="14">
+        <v>6432.04</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
       <c r="A19" s="2">
         <v>2021.5</v>
       </c>
@@ -1598,7 +1666,7 @@
         <v>282000000</v>
       </c>
       <c r="D19" s="2">
-        <f>ROUND(C19/B19*100,2)</f>
+        <f t="shared" si="10"/>
         <v>5.52</v>
       </c>
       <c r="E19" s="4">
@@ -1608,7 +1676,7 @@
         <v>159900000</v>
       </c>
       <c r="G19" s="2">
-        <f>ROUND(F19/B19*100,2)</f>
+        <f t="shared" si="5"/>
         <v>3.13</v>
       </c>
       <c r="H19" s="2">
@@ -1621,14 +1689,14 @@
         <v>951900000</v>
       </c>
       <c r="K19" s="2">
-        <f>ROUND(J19/I19*100,2)</f>
+        <f t="shared" si="11"/>
         <v>37.6</v>
       </c>
       <c r="L19" s="2">
         <v>0</v>
       </c>
       <c r="M19" s="2">
-        <f>O19-P19</f>
+        <f t="shared" si="12"/>
         <v>505.6</v>
       </c>
       <c r="N19" s="2">
@@ -1643,8 +1711,11 @@
       <c r="Q19" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:17">
+      <c r="R19" s="14">
+        <v>6839.65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
       <c r="A20" s="2">
         <v>2022.5</v>
       </c>
@@ -1655,7 +1726,7 @@
         <v>171500000</v>
       </c>
       <c r="D20" s="2">
-        <f>ROUND(C20/B20*100,2)</f>
+        <f t="shared" si="10"/>
         <v>3.1</v>
       </c>
       <c r="E20" s="4">
@@ -1665,7 +1736,7 @@
         <v>166700000</v>
       </c>
       <c r="G20" s="2">
-        <f>ROUND(F20/B20*100,2)</f>
+        <f t="shared" si="5"/>
         <v>3.01</v>
       </c>
       <c r="H20" s="2">
@@ -1678,14 +1749,14 @@
         <v>772700000</v>
       </c>
       <c r="K20" s="2">
-        <f>ROUND(J20/I20*100,2)</f>
+        <f t="shared" si="11"/>
         <v>25.65</v>
       </c>
       <c r="L20" s="2">
         <v>0</v>
       </c>
       <c r="M20" s="2">
-        <f>O20-P20</f>
+        <f t="shared" si="12"/>
         <v>32.300000000000011</v>
       </c>
       <c r="N20" s="2">
@@ -1700,8 +1771,11 @@
       <c r="Q20" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:17">
+      <c r="R20" s="14">
+        <v>7434.27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
       <c r="A21" s="2">
         <v>2023.5</v>
       </c>
@@ -1712,7 +1786,7 @@
         <v>325600000</v>
       </c>
       <c r="D21" s="2">
-        <f>ROUND(C21/B21*100,2)</f>
+        <f t="shared" si="10"/>
         <v>5.31</v>
       </c>
       <c r="E21" s="4">
@@ -1722,7 +1796,7 @@
         <v>206900000</v>
       </c>
       <c r="G21" s="2">
-        <f>ROUND(F21/B21*100,2)</f>
+        <f t="shared" si="5"/>
         <v>3.37</v>
       </c>
       <c r="H21" s="2">
@@ -1735,14 +1809,14 @@
         <v>828700000</v>
       </c>
       <c r="K21" s="2">
-        <f>ROUND(J21/I21*100,2)</f>
+        <f t="shared" si="11"/>
         <v>29.1</v>
       </c>
       <c r="L21" s="2">
         <v>0</v>
       </c>
       <c r="M21" s="2">
-        <f>O21-P21</f>
+        <f t="shared" si="12"/>
         <v>268.10000000000002</v>
       </c>
       <c r="N21" s="2">
@@ -1757,8 +1831,11 @@
       <c r="Q21" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:17">
+      <c r="R21" s="14">
+        <v>7725.17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
       <c r="A22" s="2">
         <v>2024.5</v>
       </c>
@@ -1769,7 +1846,7 @@
         <v>278600000</v>
       </c>
       <c r="D22" s="2">
-        <f>ROUND(C22/B22*100,2)</f>
+        <f t="shared" si="10"/>
         <v>4.3</v>
       </c>
       <c r="E22" s="4">
@@ -1779,7 +1856,7 @@
         <v>287600000</v>
       </c>
       <c r="G22" s="2">
-        <f>ROUND(F22/B22*100,2)</f>
+        <f t="shared" si="5"/>
         <v>4.4400000000000004</v>
       </c>
       <c r="H22" s="2">
@@ -1792,14 +1869,14 @@
         <v>618700000</v>
       </c>
       <c r="K22" s="2">
-        <f>ROUND(J22/I22*100,2)</f>
+        <f t="shared" si="11"/>
         <v>20.41</v>
       </c>
       <c r="L22" s="2">
         <v>1</v>
       </c>
       <c r="M22" s="2">
-        <f>O22-P22</f>
+        <f t="shared" si="12"/>
         <v>54.900000000000034</v>
       </c>
       <c r="N22" s="2">
@@ -1814,8 +1891,11 @@
       <c r="Q22" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:17">
+      <c r="R22" s="14">
+        <v>7918.4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18">
       <c r="A28" s="2"/>
       <c r="B28" s="6"/>
       <c r="C28" s="4"/>
@@ -1830,7 +1910,7 @@
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
     </row>
-    <row r="29" spans="1:17">
+    <row r="29" spans="1:18">
       <c r="A29" s="2"/>
       <c r="B29" s="6"/>
       <c r="C29" s="4"/>
@@ -1845,7 +1925,7 @@
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
     </row>
-    <row r="30" spans="1:17">
+    <row r="30" spans="1:18">
       <c r="A30" s="2"/>
       <c r="B30" s="6"/>
       <c r="C30" s="4"/>
@@ -1860,7 +1940,7 @@
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
     </row>
-    <row r="31" spans="1:17">
+    <row r="31" spans="1:18">
       <c r="A31" s="2"/>
       <c r="B31" s="6"/>
       <c r="C31" s="4"/>
@@ -1957,7 +2037,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q35"/>
+  <dimension ref="A1:R35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
@@ -1975,9 +2055,10 @@
     <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="18.75" customHeight="1">
+    <row r="1" spans="1:18" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2026,11 +2107,14 @@
       <c r="P1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="14" t="s">
+      <c r="Q1" s="5" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:17">
+      <c r="R1" s="13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2" s="2">
         <v>2015</v>
       </c>
@@ -2086,8 +2170,11 @@
       <c r="Q2" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:17">
+      <c r="R2" s="2">
+        <v>6641.77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3" s="2">
         <v>2016</v>
       </c>
@@ -2143,8 +2230,11 @@
       <c r="Q3" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:17">
+      <c r="R3" s="2">
+        <v>6335.38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" s="2">
         <v>2017</v>
       </c>
@@ -2155,7 +2245,7 @@
         <v>246200000</v>
       </c>
       <c r="D4" s="2">
-        <f>ROUND(C4/B4*100,2)</f>
+        <f t="shared" ref="D4:D12" si="4">ROUND(C4/B4*100,2)</f>
         <v>10.35</v>
       </c>
       <c r="E4" s="4">
@@ -2165,7 +2255,7 @@
         <v>184580000</v>
       </c>
       <c r="G4" s="2">
-        <f>ROUND(F4/B4*100,2)</f>
+        <f t="shared" ref="G4:G12" si="5">ROUND(F4/B4*100,2)</f>
         <v>7.76</v>
       </c>
       <c r="H4" s="2">
@@ -2178,14 +2268,14 @@
         <v>234335000</v>
       </c>
       <c r="K4" s="2">
-        <f>ROUND(J4/I4*100,2)</f>
+        <f t="shared" ref="K4:K12" si="6">ROUND(J4/I4*100,2)</f>
         <v>40.479999999999997</v>
       </c>
       <c r="L4" s="2">
         <v>1.55</v>
       </c>
       <c r="M4" s="2">
-        <f>O4-P4</f>
+        <f t="shared" ref="M4:M13" si="7">O4-P4</f>
         <v>55.899999999999977</v>
       </c>
       <c r="N4" s="2">
@@ -2200,8 +2290,11 @@
       <c r="Q4" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:17">
+      <c r="R4" s="2">
+        <v>6842.83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5" s="2">
         <v>2018</v>
       </c>
@@ -2212,7 +2305,7 @@
         <v>295900000</v>
       </c>
       <c r="D5" s="2">
-        <f>ROUND(C5/B5*100,2)</f>
+        <f t="shared" si="4"/>
         <v>9.36</v>
       </c>
       <c r="E5" s="4">
@@ -2222,7 +2315,7 @@
         <v>236400000</v>
       </c>
       <c r="G5" s="2">
-        <f>ROUND(F5/B5*100,2)</f>
+        <f t="shared" si="5"/>
         <v>7.48</v>
       </c>
       <c r="H5" s="2">
@@ -2235,14 +2328,14 @@
         <v>334600000</v>
       </c>
       <c r="K5" s="2">
-        <f>ROUND(J5/I5*100,2)</f>
+        <f t="shared" si="6"/>
         <v>40.11</v>
       </c>
       <c r="L5" s="2">
         <v>1.63</v>
       </c>
       <c r="M5" s="2">
-        <f>O5-P5</f>
+        <f t="shared" si="7"/>
         <v>134.60000000000002</v>
       </c>
       <c r="N5" s="2">
@@ -2257,8 +2350,11 @@
       <c r="Q5" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:17">
+      <c r="R5" s="2">
+        <v>7428.21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6" s="2">
         <v>2019</v>
       </c>
@@ -2269,7 +2365,7 @@
         <v>346200000</v>
       </c>
       <c r="D6" s="2">
-        <f>ROUND(C6/B6*100,2)</f>
+        <f t="shared" si="4"/>
         <v>7.34</v>
       </c>
       <c r="E6" s="4">
@@ -2279,7 +2375,7 @@
         <v>264200000</v>
       </c>
       <c r="G6" s="2">
-        <f>ROUND(F6/B6*100,2)</f>
+        <f t="shared" si="5"/>
         <v>5.6</v>
       </c>
       <c r="H6" s="2">
@@ -2292,14 +2388,14 @@
         <v>237700000</v>
       </c>
       <c r="K6" s="2">
-        <f>ROUND(J6/I6*100,2)</f>
+        <f t="shared" si="6"/>
         <v>22.07</v>
       </c>
       <c r="L6" s="2">
         <v>1.71</v>
       </c>
       <c r="M6" s="2">
-        <f>O6-P6</f>
+        <f t="shared" si="7"/>
         <v>-173.19999999999993</v>
       </c>
       <c r="N6" s="2">
@@ -2314,8 +2410,11 @@
       <c r="Q6" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:17">
+      <c r="R6" s="14">
+        <v>7276.89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
       <c r="A7" s="2">
         <v>2020</v>
       </c>
@@ -2326,7 +2425,7 @@
         <v>426600000</v>
       </c>
       <c r="D7" s="2">
-        <f>ROUND(C7/B7*100,2)</f>
+        <f t="shared" si="4"/>
         <v>6.98</v>
       </c>
       <c r="E7" s="4">
@@ -2336,7 +2435,7 @@
         <v>250700000</v>
       </c>
       <c r="G7" s="2">
-        <f>ROUND(F7/B7*100,2)</f>
+        <f t="shared" si="5"/>
         <v>4.0999999999999996</v>
       </c>
       <c r="H7" s="2">
@@ -2349,14 +2448,14 @@
         <v>460300000</v>
       </c>
       <c r="K7" s="2">
-        <f>ROUND(J7/I7*100,2)</f>
+        <f t="shared" si="6"/>
         <v>35.700000000000003</v>
       </c>
       <c r="L7" s="2">
         <v>0.28000000000000003</v>
       </c>
       <c r="M7" s="2">
-        <f>O7-P7</f>
+        <f t="shared" si="7"/>
         <v>592.29999999999995</v>
       </c>
       <c r="N7" s="2">
@@ -2371,8 +2470,11 @@
       <c r="Q7" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:17">
+      <c r="R7" s="14">
+        <v>7341.89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
       <c r="A8" s="2">
         <v>2021</v>
       </c>
@@ -2383,7 +2485,7 @@
         <v>385500000</v>
       </c>
       <c r="D8" s="2">
-        <f>ROUND(C8/B8*100,2)</f>
+        <f t="shared" si="4"/>
         <v>6.25</v>
       </c>
       <c r="E8" s="4">
@@ -2393,7 +2495,7 @@
         <v>229200000</v>
       </c>
       <c r="G8" s="2">
-        <f>ROUND(F8/B8*100,2)</f>
+        <f t="shared" si="5"/>
         <v>3.72</v>
       </c>
       <c r="H8" s="2">
@@ -2406,14 +2508,14 @@
         <v>948700000</v>
       </c>
       <c r="K8" s="2">
-        <f>ROUND(J8/I8*100,2)</f>
+        <f t="shared" si="6"/>
         <v>63.4</v>
       </c>
       <c r="L8" s="2">
         <v>1.44</v>
       </c>
       <c r="M8" s="2">
-        <f>O8-P8</f>
+        <f t="shared" si="7"/>
         <v>727.89999999999986</v>
       </c>
       <c r="N8" s="2">
@@ -2428,8 +2530,11 @@
       <c r="Q8" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:17">
+      <c r="R8" s="14">
+        <v>6122.66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
       <c r="A9" s="2">
         <v>2022</v>
       </c>
@@ -2440,7 +2545,7 @@
         <v>721200000</v>
       </c>
       <c r="D9" s="2">
-        <f>ROUND(C9/B9*100,2)</f>
+        <f t="shared" si="4"/>
         <v>8.42</v>
       </c>
       <c r="E9" s="4">
@@ -2450,7 +2555,7 @@
         <v>459600000</v>
       </c>
       <c r="G9" s="2">
-        <f>ROUND(F9/B9*100,2)</f>
+        <f t="shared" si="5"/>
         <v>5.37</v>
       </c>
       <c r="H9" s="2">
@@ -2463,14 +2568,14 @@
         <v>1280400000</v>
       </c>
       <c r="K9" s="2">
-        <f>ROUND(J9/I9*100,2)</f>
+        <f t="shared" si="6"/>
         <v>54.73</v>
       </c>
       <c r="L9" s="2">
         <v>0.35</v>
       </c>
       <c r="M9" s="2">
-        <f>O9-P9</f>
+        <f t="shared" si="7"/>
         <v>418.80000000000007</v>
       </c>
       <c r="N9" s="2">
@@ -2485,8 +2590,11 @@
       <c r="Q9" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:17">
+      <c r="R9" s="14">
+        <v>7159.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
       <c r="A10" s="2">
         <v>2023</v>
       </c>
@@ -2497,7 +2605,7 @@
         <v>509800000</v>
       </c>
       <c r="D10" s="2">
-        <f>ROUND(C10/B10*100,2)</f>
+        <f t="shared" si="4"/>
         <v>5.03</v>
       </c>
       <c r="E10" s="4">
@@ -2507,7 +2615,7 @@
         <v>226700000</v>
       </c>
       <c r="G10" s="2">
-        <f>ROUND(F10/B10*100,2)</f>
+        <f t="shared" si="5"/>
         <v>2.2400000000000002</v>
       </c>
       <c r="H10" s="2">
@@ -2520,14 +2628,14 @@
         <v>1548900000</v>
       </c>
       <c r="K10" s="2">
-        <f>ROUND(J10/I10*100,2)</f>
+        <f t="shared" si="6"/>
         <v>58.82</v>
       </c>
       <c r="L10" s="2">
         <v>0.8</v>
       </c>
       <c r="M10" s="2">
-        <f>O10-P10</f>
+        <f t="shared" si="7"/>
         <v>759.6</v>
       </c>
       <c r="N10" s="2">
@@ -2542,8 +2650,11 @@
       <c r="Q10" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:17">
+      <c r="R10" s="14">
+        <v>7283.02</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
       <c r="A11" s="2">
         <v>2024</v>
       </c>
@@ -2554,7 +2665,7 @@
         <v>927000000</v>
       </c>
       <c r="D11" s="2">
-        <f>ROUND(C11/B11*100,2)</f>
+        <f t="shared" si="4"/>
         <v>8.7899999999999991</v>
       </c>
       <c r="E11" s="4">
@@ -2564,7 +2675,7 @@
         <v>605000000</v>
       </c>
       <c r="G11" s="2">
-        <f>ROUND(F11/B11*100,2)</f>
+        <f t="shared" si="5"/>
         <v>5.74</v>
       </c>
       <c r="H11" s="2">
@@ -2577,14 +2688,14 @@
         <v>1102000000</v>
       </c>
       <c r="K11" s="2">
-        <f>ROUND(J11/I11*100,2)</f>
+        <f t="shared" si="6"/>
         <v>38.409999999999997</v>
       </c>
       <c r="L11" s="2">
         <v>0.9</v>
       </c>
       <c r="M11" s="2">
-        <f>O11-P11</f>
+        <f t="shared" si="7"/>
         <v>596</v>
       </c>
       <c r="N11" s="2">
@@ -2599,8 +2710,11 @@
       <c r="Q11" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:17">
+      <c r="R11" s="14">
+        <v>7508.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
       <c r="A12" s="2">
         <v>2025</v>
       </c>
@@ -2611,7 +2725,7 @@
         <v>903000000</v>
       </c>
       <c r="D12" s="2">
-        <f>ROUND(C12/B12*100,2)</f>
+        <f t="shared" si="4"/>
         <v>7.88</v>
       </c>
       <c r="E12" s="4">
@@ -2621,7 +2735,7 @@
         <v>540000000</v>
       </c>
       <c r="G12" s="2">
-        <f>ROUND(F12/B12*100,2)</f>
+        <f t="shared" si="5"/>
         <v>4.71</v>
       </c>
       <c r="H12" s="2">
@@ -2634,14 +2748,14 @@
         <v>695000000</v>
       </c>
       <c r="K12" s="2">
-        <f>ROUND(J12/I12*100,2)</f>
+        <f t="shared" si="6"/>
         <v>20.61</v>
       </c>
       <c r="L12" s="2">
         <v>1</v>
       </c>
       <c r="M12" s="2">
-        <f>O12-P12</f>
+        <f t="shared" si="7"/>
         <v>-266</v>
       </c>
       <c r="N12" s="2">
@@ -2656,8 +2770,11 @@
       <c r="Q12" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:17">
+      <c r="R12" s="14">
+        <v>8231.6200000000008</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
       <c r="A13" s="2">
         <v>2015.5</v>
       </c>
@@ -2668,7 +2785,7 @@
         <v>45720000</v>
       </c>
       <c r="D13" s="2">
-        <f t="shared" ref="D13:D14" si="4">ROUND(C13/B13*100,2)</f>
+        <f t="shared" ref="D13:D14" si="8">ROUND(C13/B13*100,2)</f>
         <v>5.65</v>
       </c>
       <c r="E13" s="4">
@@ -2678,7 +2795,7 @@
         <v>34414000</v>
       </c>
       <c r="G13" s="2">
-        <f t="shared" ref="G13:G14" si="5">ROUND(F13/B13*100,2)</f>
+        <f t="shared" ref="G13:G14" si="9">ROUND(F13/B13*100,2)</f>
         <v>4.25</v>
       </c>
       <c r="H13" s="2">
@@ -2691,14 +2808,14 @@
         <v>154818000</v>
       </c>
       <c r="K13" s="2">
-        <f t="shared" ref="K13:K14" si="6">ROUND(J13/I13*100,2)</f>
+        <f t="shared" ref="K13:K14" si="10">ROUND(J13/I13*100,2)</f>
         <v>46.93</v>
       </c>
       <c r="L13" s="2">
         <v>1.41</v>
       </c>
       <c r="M13" s="2">
-        <f>O13-P13</f>
+        <f t="shared" si="7"/>
         <v>24.700000000000003</v>
       </c>
       <c r="N13" s="2">
@@ -2713,8 +2830,11 @@
       <c r="Q13" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17">
+      <c r="R13" s="14">
+        <v>6855.45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
       <c r="A14" s="2">
         <v>2016.5</v>
       </c>
@@ -2725,7 +2845,7 @@
         <v>77650000</v>
       </c>
       <c r="D14" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
       <c r="E14" s="4">
@@ -2735,7 +2855,7 @@
         <v>60019000</v>
       </c>
       <c r="G14" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>6.19</v>
       </c>
       <c r="H14" s="2">
@@ -2748,14 +2868,14 @@
         <v>240044000</v>
       </c>
       <c r="K14" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>52.17</v>
       </c>
       <c r="L14" s="2">
         <v>1.48</v>
       </c>
       <c r="M14" s="2">
-        <f t="shared" ref="M14:M15" si="7">O14-P14</f>
+        <f t="shared" ref="M14" si="11">O14-P14</f>
         <v>21.399999999999991</v>
       </c>
       <c r="N14" s="2">
@@ -2770,8 +2890,11 @@
       <c r="Q14" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17">
+      <c r="R14" s="14">
+        <v>6097.14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
       <c r="A15" s="2">
         <v>2017.5</v>
       </c>
@@ -2782,7 +2905,7 @@
         <v>102100000</v>
       </c>
       <c r="D15" s="2">
-        <f t="shared" ref="D15:D16" si="8">ROUND(C15/B15*100,2)</f>
+        <f t="shared" ref="D15:D16" si="12">ROUND(C15/B15*100,2)</f>
         <v>7.5</v>
       </c>
       <c r="E15" s="4">
@@ -2792,7 +2915,7 @@
         <v>81100000</v>
       </c>
       <c r="G15" s="2">
-        <f>ROUND(F15/B15*100,2)</f>
+        <f t="shared" ref="G15:G22" si="13">ROUND(F15/B15*100,2)</f>
         <v>5.95</v>
       </c>
       <c r="H15" s="2">
@@ -2805,7 +2928,7 @@
         <v>230700000</v>
       </c>
       <c r="K15" s="2">
-        <f t="shared" ref="K15:K16" si="9">ROUND(J15/I15*100,2)</f>
+        <f t="shared" ref="K15:K16" si="14">ROUND(J15/I15*100,2)</f>
         <v>35.380000000000003</v>
       </c>
       <c r="L15" s="2">
@@ -2827,8 +2950,11 @@
       <c r="Q15" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17">
+      <c r="R15" s="14">
+        <v>7330.76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
       <c r="A16" s="2">
         <v>2018.5</v>
       </c>
@@ -2839,7 +2965,7 @@
         <v>123900000</v>
       </c>
       <c r="D16" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>6.71</v>
       </c>
       <c r="E16" s="4">
@@ -2849,7 +2975,7 @@
         <v>95400000</v>
       </c>
       <c r="G16" s="2">
-        <f>ROUND(F16/B16*100,2)</f>
+        <f t="shared" si="13"/>
         <v>5.17</v>
       </c>
       <c r="H16" s="2">
@@ -2862,7 +2988,7 @@
         <v>229800000</v>
       </c>
       <c r="K16" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>25.03</v>
       </c>
       <c r="L16" s="2">
@@ -2884,8 +3010,11 @@
       <c r="Q16" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:17">
+      <c r="R16" s="14">
+        <v>7450.95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
       <c r="A17" s="2">
         <v>2019.5</v>
       </c>
@@ -2896,7 +3025,7 @@
         <v>171100000</v>
       </c>
       <c r="D17" s="2">
-        <f t="shared" ref="D17:D18" si="10">ROUND(C17/B17*100,2)</f>
+        <f t="shared" ref="D17:D18" si="15">ROUND(C17/B17*100,2)</f>
         <v>6.29</v>
       </c>
       <c r="E17" s="4">
@@ -2906,7 +3035,7 @@
         <v>98000000</v>
       </c>
       <c r="G17" s="2">
-        <f>ROUND(F17/B17*100,2)</f>
+        <f t="shared" si="13"/>
         <v>3.6</v>
       </c>
       <c r="H17" s="2">
@@ -2919,14 +3048,14 @@
         <v>323500000</v>
       </c>
       <c r="K17" s="2">
-        <f t="shared" ref="K17:K18" si="11">ROUND(J17/I17*100,2)</f>
+        <f t="shared" ref="K17:K18" si="16">ROUND(J17/I17*100,2)</f>
         <v>26.36</v>
       </c>
       <c r="L17" s="2">
         <v>0.28000000000000003</v>
       </c>
       <c r="M17" s="2">
-        <f t="shared" ref="M17:M21" si="12">O17-P17</f>
+        <f t="shared" ref="M17:M18" si="17">O17-P17</f>
         <v>162.5</v>
       </c>
       <c r="N17" s="2">
@@ -2941,8 +3070,11 @@
       <c r="Q17" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:17">
+      <c r="R17" s="14">
+        <v>7208.45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
       <c r="A18" s="2">
         <v>2020.5</v>
       </c>
@@ -2953,7 +3085,7 @@
         <v>75000000</v>
       </c>
       <c r="D18" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="15"/>
         <v>2.95</v>
       </c>
       <c r="E18" s="4">
@@ -2963,7 +3095,7 @@
         <v>27100000</v>
       </c>
       <c r="G18" s="2">
-        <f>ROUND(F18/B18*100,2)</f>
+        <f t="shared" si="13"/>
         <v>1.06</v>
       </c>
       <c r="H18" s="2">
@@ -2976,14 +3108,14 @@
         <v>1068800000</v>
       </c>
       <c r="K18" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>79.7</v>
       </c>
       <c r="L18" s="2">
         <v>1.48</v>
       </c>
       <c r="M18" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v>479.90000000000003</v>
       </c>
       <c r="N18" s="2">
@@ -2998,8 +3130,11 @@
       <c r="Q18" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:17">
+      <c r="R18" s="14">
+        <v>6432.04</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
       <c r="A19" s="2">
         <v>2021.5</v>
       </c>
@@ -3010,7 +3145,7 @@
         <v>396800000</v>
       </c>
       <c r="D19" s="2">
-        <f t="shared" ref="D19:D20" si="13">ROUND(C19/B19*100,2)</f>
+        <f t="shared" ref="D19:D20" si="18">ROUND(C19/B19*100,2)</f>
         <v>10.210000000000001</v>
       </c>
       <c r="E19" s="4">
@@ -3020,7 +3155,7 @@
         <v>276800000</v>
       </c>
       <c r="G19" s="2">
-        <f>ROUND(F19/B19*100,2)</f>
+        <f t="shared" si="13"/>
         <v>7.12</v>
       </c>
       <c r="H19" s="2">
@@ -3033,7 +3168,7 @@
         <v>1259000000</v>
       </c>
       <c r="K19" s="2">
-        <f t="shared" ref="K19:K20" si="14">ROUND(J19/I19*100,2)</f>
+        <f t="shared" ref="K19:K20" si="19">ROUND(J19/I19*100,2)</f>
         <v>57.81</v>
       </c>
       <c r="L19" s="2">
@@ -3055,8 +3190,11 @@
       <c r="Q19" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:17">
+      <c r="R19" s="14">
+        <v>6839.65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
       <c r="A20" s="2">
         <v>2022.5</v>
       </c>
@@ -3067,7 +3205,7 @@
         <v>332900000</v>
       </c>
       <c r="D20" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>7.54</v>
       </c>
       <c r="E20" s="4">
@@ -3077,7 +3215,7 @@
         <v>216300000</v>
       </c>
       <c r="G20" s="2">
-        <f>ROUND(F20/B20*100,2)</f>
+        <f t="shared" si="13"/>
         <v>4.9000000000000004</v>
       </c>
       <c r="H20" s="2">
@@ -3090,7 +3228,7 @@
         <v>1096100000</v>
       </c>
       <c r="K20" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>41.19</v>
       </c>
       <c r="L20" s="2">
@@ -3112,8 +3250,11 @@
       <c r="Q20" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:17">
+      <c r="R20" s="14">
+        <v>7434.27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
       <c r="A21" s="2">
         <v>2023.5</v>
       </c>
@@ -3124,7 +3265,7 @@
         <v>374800000</v>
       </c>
       <c r="D21" s="2">
-        <f t="shared" ref="D21" si="15">ROUND(C21/B21*100,2)</f>
+        <f t="shared" ref="D21" si="20">ROUND(C21/B21*100,2)</f>
         <v>7.83</v>
       </c>
       <c r="E21" s="4">
@@ -3134,7 +3275,7 @@
         <v>257500000</v>
       </c>
       <c r="G21" s="2">
-        <f>ROUND(F21/B21*100,2)</f>
+        <f t="shared" si="13"/>
         <v>5.38</v>
       </c>
       <c r="H21" s="2">
@@ -3147,7 +3288,7 @@
         <v>1343900000</v>
       </c>
       <c r="K21" s="2">
-        <f t="shared" ref="K21" si="16">ROUND(J21/I21*100,2)</f>
+        <f t="shared" ref="K21" si="21">ROUND(J21/I21*100,2)</f>
         <v>46.85</v>
       </c>
       <c r="L21" s="2">
@@ -3169,8 +3310,11 @@
       <c r="Q21" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:17">
+      <c r="R21" s="14">
+        <v>7725.17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
       <c r="A22" s="2">
         <v>2024.5</v>
       </c>
@@ -3181,7 +3325,7 @@
         <v>292200000</v>
       </c>
       <c r="D22" s="2">
-        <f t="shared" ref="D22" si="17">ROUND(C22/B22*100,2)</f>
+        <f t="shared" ref="D22" si="22">ROUND(C22/B22*100,2)</f>
         <v>5.81</v>
       </c>
       <c r="E22" s="4">
@@ -3191,7 +3335,7 @@
         <v>52200000</v>
       </c>
       <c r="G22" s="2">
-        <f>ROUND(F22/B22*100,2)</f>
+        <f t="shared" si="13"/>
         <v>1.04</v>
       </c>
       <c r="H22" s="2">
@@ -3204,7 +3348,7 @@
         <v>879600000</v>
       </c>
       <c r="K22" s="2">
-        <f t="shared" ref="K22" si="18">ROUND(J22/I22*100,2)</f>
+        <f t="shared" ref="K22" si="23">ROUND(J22/I22*100,2)</f>
         <v>31</v>
       </c>
       <c r="L22" s="2">
@@ -3226,8 +3370,11 @@
       <c r="Q22" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:17">
+      <c r="R22" s="14">
+        <v>7918.4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -3240,7 +3387,7 @@
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
     </row>
-    <row r="28" spans="1:17">
+    <row r="28" spans="1:18">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -3253,7 +3400,7 @@
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
     </row>
-    <row r="29" spans="1:17">
+    <row r="29" spans="1:18">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -3266,7 +3413,7 @@
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
     </row>
-    <row r="31" spans="1:17">
+    <row r="31" spans="1:18">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -3279,7 +3426,7 @@
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
     </row>
-    <row r="32" spans="1:17">
+    <row r="32" spans="1:18">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -3339,7 +3486,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA31B35B-4422-43CD-BBD4-2F865077DAF3}">
-  <dimension ref="A1:Q57"/>
+  <dimension ref="A1:R57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
@@ -3357,9 +3504,10 @@
     <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3408,11 +3556,14 @@
       <c r="P1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="14" t="s">
+      <c r="Q1" s="5" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:17">
+      <c r="R1" s="13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2" s="2">
         <v>2015</v>
       </c>
@@ -3468,8 +3619,11 @@
       <c r="Q2" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:17">
+      <c r="R2" s="2">
+        <v>6641.77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3" s="2">
         <v>2016</v>
       </c>
@@ -3525,8 +3679,11 @@
       <c r="Q3" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:17">
+      <c r="R3" s="2">
+        <v>6335.38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" s="2">
         <v>2017</v>
       </c>
@@ -3582,8 +3739,11 @@
       <c r="Q4" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:17">
+      <c r="R4" s="2">
+        <v>6842.83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5" s="2">
         <v>2018</v>
       </c>
@@ -3639,8 +3799,11 @@
       <c r="Q5" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:17">
+      <c r="R5" s="2">
+        <v>7428.21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6" s="2">
         <v>2019</v>
       </c>
@@ -3696,8 +3859,11 @@
       <c r="Q6" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:17">
+      <c r="R6" s="14">
+        <v>7276.89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
       <c r="A7" s="2">
         <v>2020</v>
       </c>
@@ -3753,8 +3919,11 @@
       <c r="Q7" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:17">
+      <c r="R7" s="14">
+        <v>7341.89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
       <c r="A8" s="2">
         <v>2021</v>
       </c>
@@ -3810,8 +3979,11 @@
       <c r="Q8" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:17">
+      <c r="R8" s="14">
+        <v>6122.66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
       <c r="A9" s="2">
         <v>2022</v>
       </c>
@@ -3867,8 +4039,11 @@
       <c r="Q9" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:17">
+      <c r="R9" s="14">
+        <v>7159.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
       <c r="A10" s="2">
         <v>2023</v>
       </c>
@@ -3924,8 +4099,11 @@
       <c r="Q10" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:17">
+      <c r="R10" s="14">
+        <v>7283.02</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
       <c r="A11" s="2">
         <v>2024</v>
       </c>
@@ -3981,8 +4159,11 @@
       <c r="Q11" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:17">
+      <c r="R11" s="14">
+        <v>7508.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
       <c r="A12" s="2">
         <v>2025</v>
       </c>
@@ -4038,8 +4219,11 @@
       <c r="Q12" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:17">
+      <c r="R12" s="14">
+        <v>8231.6200000000008</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
       <c r="A13" s="2">
         <v>2015.5</v>
       </c>
@@ -4095,8 +4279,11 @@
       <c r="Q13" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17">
+      <c r="R13" s="14">
+        <v>6855.45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
       <c r="A14" s="2">
         <v>2016.5</v>
       </c>
@@ -4152,8 +4339,11 @@
       <c r="Q14" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17">
+      <c r="R14" s="14">
+        <v>6097.14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
       <c r="A15" s="2">
         <v>2017.5</v>
       </c>
@@ -4209,8 +4399,11 @@
       <c r="Q15" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17">
+      <c r="R15" s="14">
+        <v>7330.76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
       <c r="A16" s="2">
         <v>2018.5</v>
       </c>
@@ -4266,8 +4459,11 @@
       <c r="Q16" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:17">
+      <c r="R16" s="14">
+        <v>7450.95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
       <c r="A17" s="2">
         <v>2019.5</v>
       </c>
@@ -4323,8 +4519,11 @@
       <c r="Q17" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:17">
+      <c r="R17" s="14">
+        <v>7208.45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
       <c r="A18" s="2">
         <v>2020.5</v>
       </c>
@@ -4380,8 +4579,11 @@
       <c r="Q18" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:17">
+      <c r="R18" s="14">
+        <v>6432.04</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
       <c r="A19" s="2">
         <v>2021.5</v>
       </c>
@@ -4437,8 +4639,11 @@
       <c r="Q19" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:17">
+      <c r="R19" s="14">
+        <v>6839.65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
       <c r="A20" s="2">
         <v>2022.5</v>
       </c>
@@ -4494,8 +4699,11 @@
       <c r="Q20" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:17">
+      <c r="R20" s="14">
+        <v>7434.27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
       <c r="A21" s="2">
         <v>2023.5</v>
       </c>
@@ -4551,8 +4759,11 @@
       <c r="Q21" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:17">
+      <c r="R21" s="14">
+        <v>7725.17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
       <c r="A22" s="2">
         <v>2024.5</v>
       </c>
@@ -4608,8 +4819,11 @@
       <c r="Q22" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:17">
+      <c r="R22" s="14">
+        <v>7918.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -4622,7 +4836,7 @@
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
     </row>
-    <row r="26" spans="1:17">
+    <row r="26" spans="1:18">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -4635,7 +4849,7 @@
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
     </row>
-    <row r="27" spans="1:17">
+    <row r="27" spans="1:18">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -4648,7 +4862,7 @@
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
     </row>
-    <row r="28" spans="1:17">
+    <row r="28" spans="1:18">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -4661,7 +4875,7 @@
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
     </row>
-    <row r="29" spans="1:17">
+    <row r="29" spans="1:18">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -4674,7 +4888,7 @@
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
     </row>
-    <row r="30" spans="1:17">
+    <row r="30" spans="1:18">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -4687,7 +4901,7 @@
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
     </row>
-    <row r="31" spans="1:17">
+    <row r="31" spans="1:18">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -4700,7 +4914,7 @@
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
     </row>
-    <row r="32" spans="1:17">
+    <row r="32" spans="1:18">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -5001,7 +5215,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AA4EB3C-9A28-41B7-8238-3053EDD73B74}">
-  <dimension ref="A1:Q46"/>
+  <dimension ref="A1:R46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
@@ -5019,9 +5233,10 @@
     <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5070,11 +5285,14 @@
       <c r="P1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="14" t="s">
+      <c r="Q1" s="5" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:17">
+      <c r="R1" s="13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2" s="2">
         <v>2015</v>
       </c>
@@ -5130,8 +5348,11 @@
       <c r="Q2" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:17">
+      <c r="R2" s="2">
+        <v>6641.77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3" s="2">
         <v>2016</v>
       </c>
@@ -5187,8 +5408,11 @@
       <c r="Q3" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:17">
+      <c r="R3" s="2">
+        <v>6335.38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" s="2">
         <v>2017</v>
       </c>
@@ -5244,8 +5468,11 @@
       <c r="Q4" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:17">
+      <c r="R4" s="2">
+        <v>6842.83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5" s="2">
         <v>2018</v>
       </c>
@@ -5301,8 +5528,11 @@
       <c r="Q5" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:17">
+      <c r="R5" s="2">
+        <v>7428.21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6" s="2">
         <v>2019</v>
       </c>
@@ -5358,8 +5588,11 @@
       <c r="Q6" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:17">
+      <c r="R6" s="14">
+        <v>7276.89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
       <c r="A7" s="2">
         <v>2020</v>
       </c>
@@ -5415,8 +5648,11 @@
       <c r="Q7" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:17">
+      <c r="R7" s="14">
+        <v>7341.89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
       <c r="A8" s="2">
         <v>2021</v>
       </c>
@@ -5472,8 +5708,11 @@
       <c r="Q8" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:17">
+      <c r="R8" s="14">
+        <v>6122.66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
       <c r="A9" s="2">
         <v>2022</v>
       </c>
@@ -5529,8 +5768,11 @@
       <c r="Q9" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:17">
+      <c r="R9" s="14">
+        <v>7159.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
       <c r="A10" s="2">
         <v>2023</v>
       </c>
@@ -5586,8 +5828,11 @@
       <c r="Q10" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:17">
+      <c r="R10" s="14">
+        <v>7283.02</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
       <c r="A11" s="2">
         <v>2024</v>
       </c>
@@ -5643,8 +5888,11 @@
       <c r="Q11" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:17">
+      <c r="R11" s="14">
+        <v>7508.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
       <c r="A12" s="2">
         <v>2025</v>
       </c>
@@ -5700,8 +5948,11 @@
       <c r="Q12" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:17">
+      <c r="R12" s="14">
+        <v>8231.6200000000008</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
       <c r="A13" s="2">
         <v>2015.5</v>
       </c>
@@ -5757,8 +6008,11 @@
       <c r="Q13" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17">
+      <c r="R13" s="14">
+        <v>6855.45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
       <c r="A14" s="2">
         <v>2016.5</v>
       </c>
@@ -5814,8 +6068,11 @@
       <c r="Q14" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17">
+      <c r="R14" s="14">
+        <v>6097.14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
       <c r="A15" s="2">
         <v>2017.5</v>
       </c>
@@ -5871,8 +6128,11 @@
       <c r="Q15" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17">
+      <c r="R15" s="14">
+        <v>7330.76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
       <c r="A16" s="2">
         <v>2018.5</v>
       </c>
@@ -5928,8 +6188,11 @@
       <c r="Q16" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:17">
+      <c r="R16" s="14">
+        <v>7450.95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
       <c r="A17" s="2">
         <v>2019.5</v>
       </c>
@@ -5985,8 +6248,11 @@
       <c r="Q17" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:17">
+      <c r="R17" s="14">
+        <v>7208.45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
       <c r="A18" s="2">
         <v>2020.5</v>
       </c>
@@ -6042,8 +6308,11 @@
       <c r="Q18" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:17">
+      <c r="R18" s="14">
+        <v>6432.04</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
       <c r="A19" s="2">
         <v>2021.5</v>
       </c>
@@ -6099,8 +6368,11 @@
       <c r="Q19" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:17">
+      <c r="R19" s="14">
+        <v>6839.65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
       <c r="A20" s="2">
         <v>2022.5</v>
       </c>
@@ -6156,8 +6428,11 @@
       <c r="Q20" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:17">
+      <c r="R20" s="14">
+        <v>7434.27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
       <c r="A21" s="2">
         <v>2023.5</v>
       </c>
@@ -6213,8 +6488,11 @@
       <c r="Q21" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:17">
+      <c r="R21" s="14">
+        <v>7725.17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
       <c r="A22" s="2">
         <v>2024.5</v>
       </c>
@@ -6270,8 +6548,11 @@
       <c r="Q22" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:17">
+      <c r="R22" s="14">
+        <v>7918.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -6284,7 +6565,7 @@
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
     </row>
-    <row r="26" spans="1:17">
+    <row r="26" spans="1:18">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -6297,7 +6578,7 @@
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
     </row>
-    <row r="27" spans="1:17">
+    <row r="27" spans="1:18">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -6310,7 +6591,7 @@
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
     </row>
-    <row r="28" spans="1:17">
+    <row r="28" spans="1:18">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -6323,7 +6604,7 @@
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
     </row>
-    <row r="29" spans="1:17">
+    <row r="29" spans="1:18">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -6336,7 +6617,7 @@
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
     </row>
-    <row r="30" spans="1:17">
+    <row r="30" spans="1:18">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -6349,7 +6630,7 @@
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
     </row>
-    <row r="31" spans="1:17">
+    <row r="31" spans="1:18">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -6362,7 +6643,7 @@
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
     </row>
-    <row r="32" spans="1:17">
+    <row r="32" spans="1:18">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -6512,7 +6793,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E59D2B3-8ABF-4688-A725-32854CE92AB1}">
-  <dimension ref="A1:Q66"/>
+  <dimension ref="A1:R66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
@@ -6530,9 +6811,10 @@
     <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6581,11 +6863,14 @@
       <c r="P1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="14" t="s">
+      <c r="Q1" s="5" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:17">
+      <c r="R1" s="13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2" s="2">
         <v>2015</v>
       </c>
@@ -6641,8 +6926,11 @@
       <c r="Q2" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:17">
+      <c r="R2" s="2">
+        <v>6641.77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3" s="2">
         <v>2016</v>
       </c>
@@ -6698,8 +6986,11 @@
       <c r="Q3" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:17">
+      <c r="R3" s="2">
+        <v>6335.38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" s="2">
         <v>2017</v>
       </c>
@@ -6755,8 +7046,11 @@
       <c r="Q4" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:17">
+      <c r="R4" s="2">
+        <v>6842.83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5" s="2">
         <v>2018</v>
       </c>
@@ -6812,8 +7106,11 @@
       <c r="Q5" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:17">
+      <c r="R5" s="2">
+        <v>7428.21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6" s="2">
         <v>2019</v>
       </c>
@@ -6869,8 +7166,11 @@
       <c r="Q6" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:17">
+      <c r="R6" s="14">
+        <v>7276.89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
       <c r="A7" s="2">
         <v>2020</v>
       </c>
@@ -6926,8 +7226,11 @@
       <c r="Q7" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:17">
+      <c r="R7" s="14">
+        <v>7341.89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
       <c r="A8" s="2">
         <v>2021</v>
       </c>
@@ -6983,8 +7286,11 @@
       <c r="Q8" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:17">
+      <c r="R8" s="14">
+        <v>6122.66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
       <c r="A9" s="2">
         <v>2022</v>
       </c>
@@ -7040,8 +7346,11 @@
       <c r="Q9" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:17">
+      <c r="R9" s="14">
+        <v>7159.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
       <c r="A10" s="2">
         <v>2023</v>
       </c>
@@ -7097,8 +7406,11 @@
       <c r="Q10" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:17">
+      <c r="R10" s="14">
+        <v>7283.02</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
       <c r="A11" s="2">
         <v>2024</v>
       </c>
@@ -7154,8 +7466,11 @@
       <c r="Q11" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:17">
+      <c r="R11" s="14">
+        <v>7508.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
       <c r="A12" s="2">
         <v>2025</v>
       </c>
@@ -7211,8 +7526,11 @@
       <c r="Q12" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:17">
+      <c r="R12" s="14">
+        <v>8231.6200000000008</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
       <c r="A13" s="2">
         <v>2015.5</v>
       </c>
@@ -7268,8 +7586,11 @@
       <c r="Q13" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17">
+      <c r="R13" s="14">
+        <v>6855.45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
       <c r="A14" s="2">
         <v>2016.5</v>
       </c>
@@ -7325,8 +7646,11 @@
       <c r="Q14" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17">
+      <c r="R14" s="14">
+        <v>6097.14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
       <c r="A15" s="2">
         <v>2017.5</v>
       </c>
@@ -7382,8 +7706,11 @@
       <c r="Q15" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17">
+      <c r="R15" s="14">
+        <v>7330.76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
       <c r="A16" s="2">
         <v>2018.5</v>
       </c>
@@ -7439,8 +7766,11 @@
       <c r="Q16" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:17">
+      <c r="R16" s="14">
+        <v>7450.95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
       <c r="A17" s="2">
         <v>2019.5</v>
       </c>
@@ -7496,8 +7826,11 @@
       <c r="Q17" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:17">
+      <c r="R17" s="14">
+        <v>7208.45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
       <c r="A18" s="2">
         <v>2020.5</v>
       </c>
@@ -7553,8 +7886,11 @@
       <c r="Q18" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:17">
+      <c r="R18" s="14">
+        <v>6432.04</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
       <c r="A19" s="2">
         <v>2021.5</v>
       </c>
@@ -7610,8 +7946,11 @@
       <c r="Q19" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:17">
+      <c r="R19" s="14">
+        <v>6839.65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
       <c r="A20" s="2">
         <v>2022.5</v>
       </c>
@@ -7667,8 +8006,11 @@
       <c r="Q20" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:17">
+      <c r="R20" s="14">
+        <v>7434.27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
       <c r="A21" s="2">
         <v>2023.5</v>
       </c>
@@ -7724,8 +8066,11 @@
       <c r="Q21" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:17">
+      <c r="R21" s="14">
+        <v>7725.17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
       <c r="A22" s="2">
         <v>2024.5</v>
       </c>
@@ -7780,6 +8125,9 @@
       </c>
       <c r="Q22" s="2">
         <v>0</v>
+      </c>
+      <c r="R22" s="14">
+        <v>7918.4</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -8149,7 +8497,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D121696-2BC3-4155-B968-D8988001A6F6}">
-  <dimension ref="A1:Q48"/>
+  <dimension ref="A1:R48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
@@ -8166,9 +8514,10 @@
     <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17.42578125" customWidth="1"/>
     <col min="17" max="17" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8217,11 +8566,14 @@
       <c r="P1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="14" t="s">
+      <c r="Q1" s="5" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:17">
+      <c r="R1" s="13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2" s="2">
         <v>2015</v>
       </c>
@@ -8277,8 +8629,11 @@
       <c r="Q2" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:17">
+      <c r="R2" s="2">
+        <v>6641.77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3" s="2">
         <v>2016</v>
       </c>
@@ -8334,8 +8689,11 @@
       <c r="Q3" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:17">
+      <c r="R3" s="2">
+        <v>6335.38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" s="2">
         <v>2017</v>
       </c>
@@ -8391,8 +8749,11 @@
       <c r="Q4" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:17">
+      <c r="R4" s="2">
+        <v>6842.83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5" s="2">
         <v>2018</v>
       </c>
@@ -8448,8 +8809,11 @@
       <c r="Q5" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:17">
+      <c r="R5" s="2">
+        <v>7428.21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6" s="2">
         <v>2019</v>
       </c>
@@ -8505,8 +8869,11 @@
       <c r="Q6" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:17">
+      <c r="R6" s="14">
+        <v>7276.89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
       <c r="A7" s="2">
         <v>2020</v>
       </c>
@@ -8562,8 +8929,11 @@
       <c r="Q7" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:17">
+      <c r="R7" s="14">
+        <v>7341.89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
       <c r="A8" s="2">
         <v>2021</v>
       </c>
@@ -8619,8 +8989,11 @@
       <c r="Q8" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:17">
+      <c r="R8" s="14">
+        <v>6122.66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
       <c r="A9" s="2">
         <v>2022</v>
       </c>
@@ -8676,8 +9049,11 @@
       <c r="Q9" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:17">
+      <c r="R9" s="14">
+        <v>7159.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
       <c r="A10" s="2">
         <v>2023</v>
       </c>
@@ -8733,8 +9109,11 @@
       <c r="Q10" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:17">
+      <c r="R10" s="14">
+        <v>7283.02</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
       <c r="A11" s="2">
         <v>2024</v>
       </c>
@@ -8790,8 +9169,11 @@
       <c r="Q11" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:17">
+      <c r="R11" s="14">
+        <v>7508.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
       <c r="A12" s="2">
         <v>2025</v>
       </c>
@@ -8847,8 +9229,11 @@
       <c r="Q12" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:17">
+      <c r="R12" s="14">
+        <v>8231.6200000000008</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
       <c r="A13" s="2">
         <v>2015.5</v>
       </c>
@@ -8904,8 +9289,11 @@
       <c r="Q13" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17">
+      <c r="R13" s="14">
+        <v>6855.45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
       <c r="A14" s="2">
         <v>2016.5</v>
       </c>
@@ -8961,8 +9349,11 @@
       <c r="Q14" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17">
+      <c r="R14" s="14">
+        <v>6097.14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
       <c r="A15" s="2">
         <v>2017.5</v>
       </c>
@@ -9018,8 +9409,11 @@
       <c r="Q15" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17">
+      <c r="R15" s="14">
+        <v>7330.76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
       <c r="A16" s="2">
         <v>2018.5</v>
       </c>
@@ -9075,8 +9469,11 @@
       <c r="Q16" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:17">
+      <c r="R16" s="14">
+        <v>7450.95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
       <c r="A17" s="2">
         <v>2019.5</v>
       </c>
@@ -9132,8 +9529,11 @@
       <c r="Q17" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:17">
+      <c r="R17" s="14">
+        <v>7208.45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
       <c r="A18" s="2">
         <v>2020.5</v>
       </c>
@@ -9189,8 +9589,11 @@
       <c r="Q18" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:17">
+      <c r="R18" s="14">
+        <v>6432.04</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
       <c r="A19" s="2">
         <v>2021.5</v>
       </c>
@@ -9246,8 +9649,11 @@
       <c r="Q19" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:17">
+      <c r="R19" s="14">
+        <v>6839.65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
       <c r="A20" s="2">
         <v>2022.5</v>
       </c>
@@ -9303,8 +9709,11 @@
       <c r="Q20" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:17">
+      <c r="R20" s="14">
+        <v>7434.27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
       <c r="A21" s="2">
         <v>2023.5</v>
       </c>
@@ -9360,8 +9769,11 @@
       <c r="Q21" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:17">
+      <c r="R21" s="14">
+        <v>7725.17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
       <c r="A22" s="2">
         <v>2024.5</v>
       </c>
@@ -9417,8 +9829,11 @@
       <c r="Q22" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:17">
+      <c r="R22" s="14">
+        <v>7918.4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -9432,7 +9847,7 @@
       <c r="M24" s="2"/>
       <c r="O24" s="2"/>
     </row>
-    <row r="25" spans="1:17">
+    <row r="25" spans="1:18">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -9446,7 +9861,7 @@
       <c r="M25" s="2"/>
       <c r="O25" s="2"/>
     </row>
-    <row r="26" spans="1:17">
+    <row r="26" spans="1:18">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -9460,7 +9875,7 @@
       <c r="M26" s="2"/>
       <c r="O26" s="2"/>
     </row>
-    <row r="27" spans="1:17">
+    <row r="27" spans="1:18">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -9474,7 +9889,7 @@
       <c r="M27" s="2"/>
       <c r="O27" s="2"/>
     </row>
-    <row r="28" spans="1:17">
+    <row r="28" spans="1:18">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -9488,7 +9903,7 @@
       <c r="M28" s="2"/>
       <c r="O28" s="2"/>
     </row>
-    <row r="29" spans="1:17">
+    <row r="29" spans="1:18">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -9502,7 +9917,7 @@
       <c r="M29" s="2"/>
       <c r="O29" s="2"/>
     </row>
-    <row r="30" spans="1:17">
+    <row r="30" spans="1:18">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -9516,7 +9931,7 @@
       <c r="M30" s="2"/>
       <c r="O30" s="2"/>
     </row>
-    <row r="31" spans="1:17">
+    <row r="31" spans="1:18">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -9530,7 +9945,7 @@
       <c r="M31" s="2"/>
       <c r="O31" s="2"/>
     </row>
-    <row r="32" spans="1:17">
+    <row r="32" spans="1:18">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -9719,7 +10134,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A6BAB55-484E-4714-8463-BF39C9DCC14A}">
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:R22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="2"/>
@@ -9739,10 +10154,11 @@
     <col min="15" max="15" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="9.140625" style="2"/>
     <col min="17" max="17" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="2"/>
+    <col min="18" max="18" width="14.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9791,11 +10207,14 @@
       <c r="P1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="14" t="s">
+      <c r="Q1" s="5" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:17">
+      <c r="R1" s="13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2" s="2">
         <v>2015</v>
       </c>
@@ -9816,7 +10235,7 @@
         <v>-5717900000</v>
       </c>
       <c r="G2" s="2">
-        <f>ROUND(F2/B2*100,2)</f>
+        <f t="shared" ref="G2:G22" si="1">ROUND(F2/B2*100,2)</f>
         <v>-8.8800000000000008</v>
       </c>
       <c r="H2" s="2">
@@ -9829,14 +10248,14 @@
         <v>2165000000</v>
       </c>
       <c r="K2" s="2">
-        <f t="shared" ref="K2" si="1">ROUND(J2/I2*100,2)</f>
+        <f t="shared" ref="K2" si="2">ROUND(J2/I2*100,2)</f>
         <v>30.62</v>
       </c>
       <c r="L2" s="2">
         <v>0</v>
       </c>
       <c r="M2" s="2">
-        <f t="shared" ref="M2:M22" si="2">O2-P2</f>
+        <f t="shared" ref="M2:M22" si="3">O2-P2</f>
         <v>-1531</v>
       </c>
       <c r="N2" s="2">
@@ -9851,8 +10270,11 @@
       <c r="Q2" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:17">
+      <c r="R2" s="2">
+        <v>6641.77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3" s="2">
         <v>2016</v>
       </c>
@@ -9863,7 +10285,7 @@
         <v>1072000000</v>
       </c>
       <c r="D3" s="2">
-        <f t="shared" ref="D3:D12" si="3">ROUND(C3/B3*100,2)</f>
+        <f t="shared" ref="D3:D12" si="4">ROUND(C3/B3*100,2)</f>
         <v>1.99</v>
       </c>
       <c r="E3" s="4">
@@ -9873,7 +10295,7 @@
         <v>256000000</v>
       </c>
       <c r="G3" s="2">
-        <f>ROUND(F3/B3*100,2)</f>
+        <f t="shared" si="1"/>
         <v>0.47</v>
       </c>
       <c r="H3" s="2">
@@ -9886,14 +10308,14 @@
         <v>3082000000</v>
       </c>
       <c r="K3" s="2">
-        <f t="shared" ref="K3:K12" si="4">ROUND(J3/I3*100,2)</f>
+        <f t="shared" ref="K3:K12" si="5">ROUND(J3/I3*100,2)</f>
         <v>35.770000000000003</v>
       </c>
       <c r="L3" s="2">
         <v>3.22</v>
       </c>
       <c r="M3" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1511</v>
       </c>
       <c r="N3" s="10">
@@ -9908,8 +10330,11 @@
       <c r="Q3" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:17">
+      <c r="R3" s="2">
+        <v>6335.38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" s="2">
         <v>2017</v>
       </c>
@@ -9920,7 +10345,7 @@
         <v>1017000000</v>
       </c>
       <c r="D4" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.82</v>
       </c>
       <c r="E4" s="4">
@@ -9930,7 +10355,7 @@
         <v>58000000</v>
       </c>
       <c r="G4" s="2">
-        <f>ROUND(F4/B4*100,2)</f>
+        <f t="shared" si="1"/>
         <v>0.1</v>
       </c>
       <c r="H4" s="2">
@@ -9943,14 +10368,14 @@
         <v>3821000000</v>
       </c>
       <c r="K4" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>59.57</v>
       </c>
       <c r="L4" s="2">
         <v>0.81</v>
       </c>
       <c r="M4" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2268</v>
       </c>
       <c r="N4" s="10">
@@ -9965,8 +10390,11 @@
       <c r="Q4" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:17">
+      <c r="R4" s="2">
+        <v>6842.83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5" s="2">
         <v>2018</v>
       </c>
@@ -9977,7 +10405,7 @@
         <v>1839000000</v>
       </c>
       <c r="D5" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.2</v>
       </c>
       <c r="E5" s="4">
@@ -9987,7 +10415,7 @@
         <v>994000000</v>
       </c>
       <c r="G5" s="2">
-        <f>ROUND(F5/B5*100,2)</f>
+        <f t="shared" si="1"/>
         <v>1.73</v>
       </c>
       <c r="H5" s="2">
@@ -10000,14 +10428,14 @@
         <v>4059000000</v>
       </c>
       <c r="K5" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>38.729999999999997</v>
       </c>
       <c r="L5" s="2">
         <v>3</v>
       </c>
       <c r="M5" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3448</v>
       </c>
       <c r="N5" s="10">
@@ -10022,8 +10450,11 @@
       <c r="Q5" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:17">
+      <c r="R5" s="2">
+        <v>7428.21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6" s="2">
         <v>2019</v>
       </c>
@@ -10034,7 +10465,7 @@
         <v>2153000000</v>
       </c>
       <c r="D6" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.37</v>
       </c>
       <c r="E6" s="4">
@@ -10044,7 +10475,7 @@
         <v>1320000000</v>
       </c>
       <c r="G6" s="2">
-        <f>ROUND(F6/B6*100,2)</f>
+        <f t="shared" si="1"/>
         <v>2.0699999999999998</v>
       </c>
       <c r="H6" s="2">
@@ -10057,14 +10488,14 @@
         <v>2916000000</v>
       </c>
       <c r="K6" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>19.66</v>
       </c>
       <c r="L6" s="2">
         <v>5.77</v>
       </c>
       <c r="M6" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>823</v>
       </c>
       <c r="N6" s="10">
@@ -10079,8 +10510,11 @@
       <c r="Q6" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:17">
+      <c r="R6" s="14">
+        <v>7276.89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
       <c r="A7" s="2">
         <v>2020</v>
       </c>
@@ -10091,7 +10525,7 @@
         <v>2206000000</v>
       </c>
       <c r="D7" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.8</v>
       </c>
       <c r="E7" s="4">
@@ -10101,7 +10535,7 @@
         <v>738000000</v>
       </c>
       <c r="G7" s="2">
-        <f>ROUND(F7/B7*100,2)</f>
+        <f t="shared" si="1"/>
         <v>1.27</v>
       </c>
       <c r="H7" s="2">
@@ -10114,14 +10548,14 @@
         <v>3031000000</v>
       </c>
       <c r="K7" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>22.67</v>
       </c>
       <c r="L7" s="2">
         <v>3.2</v>
       </c>
       <c r="M7" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2446</v>
       </c>
       <c r="N7" s="10">
@@ -10136,8 +10570,11 @@
       <c r="Q7" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:17">
+      <c r="R7" s="14">
+        <v>7341.89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
       <c r="A8" s="2">
         <v>2021</v>
       </c>
@@ -10148,7 +10585,7 @@
         <v>1736000000</v>
       </c>
       <c r="D8" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="E8" s="4">
@@ -10158,7 +10595,7 @@
         <v>721000000</v>
       </c>
       <c r="G8" s="2">
-        <f>ROUND(F8/B8*100,2)</f>
+        <f t="shared" si="1"/>
         <v>1.25</v>
       </c>
       <c r="H8" s="2">
@@ -10171,14 +10608,14 @@
         <v>1978000000</v>
       </c>
       <c r="K8" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>16.05</v>
       </c>
       <c r="L8" s="2">
         <v>9.15</v>
       </c>
       <c r="M8" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6773</v>
       </c>
       <c r="N8" s="10">
@@ -10193,8 +10630,11 @@
       <c r="Q8" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:17">
+      <c r="R8" s="14">
+        <v>6122.66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
       <c r="A9" s="2">
         <v>2022</v>
       </c>
@@ -10205,7 +10645,7 @@
         <v>2560000000</v>
       </c>
       <c r="D9" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.17</v>
       </c>
       <c r="E9" s="4">
@@ -10215,7 +10655,7 @@
         <v>1483000000</v>
       </c>
       <c r="G9" s="2">
-        <f>ROUND(F9/B9*100,2)</f>
+        <f t="shared" si="1"/>
         <v>2.42</v>
       </c>
       <c r="H9" s="2">
@@ -10228,14 +10668,14 @@
         <v>818000000</v>
       </c>
       <c r="K9" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5.23</v>
       </c>
       <c r="L9" s="2">
         <v>10.9</v>
       </c>
       <c r="M9" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2022</v>
       </c>
       <c r="N9" s="10">
@@ -10250,8 +10690,11 @@
       <c r="Q9" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:17">
+      <c r="R9" s="14">
+        <v>7159.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
       <c r="A10" s="2">
         <v>2023</v>
       </c>
@@ -10262,7 +10705,7 @@
         <v>1525000000</v>
       </c>
       <c r="D10" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.3199999999999998</v>
       </c>
       <c r="E10" s="4">
@@ -10272,7 +10715,7 @@
         <v>744000000</v>
       </c>
       <c r="G10" s="2">
-        <f>ROUND(F10/B10*100,2)</f>
+        <f t="shared" si="1"/>
         <v>1.1299999999999999</v>
       </c>
       <c r="H10" s="2">
@@ -10285,14 +10728,14 @@
         <v>1319000000</v>
       </c>
       <c r="K10" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10.78</v>
       </c>
       <c r="L10" s="2">
         <v>7.05</v>
       </c>
       <c r="M10" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3013</v>
       </c>
       <c r="N10" s="10">
@@ -10307,8 +10750,11 @@
       <c r="Q10" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:17">
+      <c r="R10" s="14">
+        <v>7283.02</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
       <c r="A11" s="2">
         <v>2024</v>
       </c>
@@ -10319,7 +10765,7 @@
         <v>2829000000</v>
       </c>
       <c r="D11" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.1500000000000004</v>
       </c>
       <c r="E11" s="4">
@@ -10329,7 +10775,7 @@
         <v>1764000000</v>
       </c>
       <c r="G11" s="2">
-        <f>ROUND(F11/B11*100,2)</f>
+        <f t="shared" si="1"/>
         <v>2.59</v>
       </c>
       <c r="H11" s="2">
@@ -10342,14 +10788,14 @@
         <v>1771000000</v>
       </c>
       <c r="K11" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>15.18</v>
       </c>
       <c r="L11" s="2">
         <v>12.1</v>
       </c>
       <c r="M11" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2139</v>
       </c>
       <c r="N11" s="10">
@@ -10364,8 +10810,11 @@
       <c r="Q11" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:17">
+      <c r="R11" s="14">
+        <v>7508.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
       <c r="A12" s="2">
         <v>2025</v>
       </c>
@@ -10376,7 +10825,7 @@
         <v>2711000000</v>
       </c>
       <c r="D12" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.88</v>
       </c>
       <c r="E12" s="4">
@@ -10386,7 +10835,7 @@
         <v>1604000000</v>
       </c>
       <c r="G12" s="2">
-        <f>ROUND(F12/B12*100,2)</f>
+        <f t="shared" si="1"/>
         <v>2.29</v>
       </c>
       <c r="H12" s="2">
@@ -10399,14 +10848,14 @@
         <v>1565000000</v>
       </c>
       <c r="K12" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>13.42</v>
       </c>
       <c r="L12" s="2">
         <v>13.7</v>
       </c>
       <c r="M12" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2481</v>
       </c>
       <c r="N12" s="10">
@@ -10421,8 +10870,11 @@
       <c r="Q12" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:17">
+      <c r="R12" s="14">
+        <v>8231.6200000000008</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
       <c r="A13" s="2">
         <v>2015.5</v>
       </c>
@@ -10433,7 +10885,7 @@
         <v>515000000</v>
       </c>
       <c r="D13" s="2">
-        <f t="shared" ref="D13:D22" si="5">ROUND(C13/B13*100,2)</f>
+        <f t="shared" ref="D13:D22" si="6">ROUND(C13/B13*100,2)</f>
         <v>1.88</v>
       </c>
       <c r="E13" s="4">
@@ -10443,7 +10895,7 @@
         <v>31000000</v>
       </c>
       <c r="G13" s="2">
-        <f>ROUND(F13/B13*100,2)</f>
+        <f t="shared" si="1"/>
         <v>0.11</v>
       </c>
       <c r="H13" s="2">
@@ -10456,14 +10908,14 @@
         <v>3355000000</v>
       </c>
       <c r="K13" s="2">
-        <f t="shared" ref="K13:K22" si="6">ROUND(J13/I13*100,2)</f>
+        <f t="shared" ref="K13:K22" si="7">ROUND(J13/I13*100,2)</f>
         <v>56.76</v>
       </c>
       <c r="L13" s="2">
         <v>0</v>
       </c>
       <c r="M13" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-1</v>
       </c>
       <c r="N13" s="10">
@@ -10478,8 +10930,11 @@
       <c r="Q13" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17">
+      <c r="R13" s="14">
+        <v>6855.45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
       <c r="A14" s="2">
         <v>2016.5</v>
       </c>
@@ -10490,7 +10945,7 @@
         <v>885000000</v>
       </c>
       <c r="D14" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.12</v>
       </c>
       <c r="E14" s="4">
@@ -10500,7 +10955,7 @@
         <v>424000000</v>
       </c>
       <c r="G14" s="2">
-        <f>ROUND(F14/B14*100,2)</f>
+        <f t="shared" si="1"/>
         <v>1.5</v>
       </c>
       <c r="H14" s="2">
@@ -10513,14 +10968,14 @@
         <v>4319000000</v>
       </c>
       <c r="K14" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>40.94</v>
       </c>
       <c r="L14" s="2">
         <v>1</v>
       </c>
       <c r="M14" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1046</v>
       </c>
       <c r="N14" s="10">
@@ -10535,8 +10990,11 @@
       <c r="Q14" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17">
+      <c r="R14" s="14">
+        <v>6097.14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
       <c r="A15" s="2">
         <v>2017.5</v>
       </c>
@@ -10547,7 +11005,7 @@
         <v>1007000000</v>
       </c>
       <c r="D15" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.17</v>
       </c>
       <c r="E15" s="4">
@@ -10557,7 +11015,7 @@
         <v>338000000</v>
       </c>
       <c r="G15" s="2">
-        <f>ROUND(F15/B15*100,2)</f>
+        <f t="shared" si="1"/>
         <v>1.07</v>
       </c>
       <c r="H15" s="2">
@@ -10570,14 +11028,14 @@
         <v>3243000000</v>
       </c>
       <c r="K15" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>25.09</v>
       </c>
       <c r="L15" s="2">
         <v>1.67</v>
       </c>
       <c r="M15" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>662</v>
       </c>
       <c r="N15" s="10">
@@ -10592,8 +11050,11 @@
       <c r="Q15" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17">
+      <c r="R15" s="14">
+        <v>7330.76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
       <c r="A16" s="2">
         <v>2018.5</v>
       </c>
@@ -10604,7 +11065,7 @@
         <v>1134000000</v>
       </c>
       <c r="D16" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.55</v>
       </c>
       <c r="E16" s="4">
@@ -10614,7 +11075,7 @@
         <v>324000000</v>
       </c>
       <c r="G16" s="2">
-        <f>ROUND(F16/B16*100,2)</f>
+        <f t="shared" si="1"/>
         <v>1.02</v>
       </c>
       <c r="H16" s="2">
@@ -10627,14 +11088,14 @@
         <v>2656000000</v>
       </c>
       <c r="K16" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>19.02</v>
       </c>
       <c r="L16" s="2">
         <v>2.65</v>
       </c>
       <c r="M16" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>971</v>
       </c>
       <c r="N16" s="10">
@@ -10649,8 +11110,11 @@
       <c r="Q16" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:17">
+      <c r="R16" s="14">
+        <v>7450.95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
       <c r="A17" s="2">
         <v>2019.5</v>
       </c>
@@ -10661,7 +11125,7 @@
         <v>1007000000</v>
       </c>
       <c r="D17" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.57</v>
       </c>
       <c r="E17" s="4">
@@ -10671,7 +11135,7 @@
         <v>397000000</v>
       </c>
       <c r="G17" s="2">
-        <f>ROUND(F17/B17*100,2)</f>
+        <f t="shared" si="1"/>
         <v>1.41</v>
       </c>
       <c r="H17" s="2">
@@ -10684,14 +11148,14 @@
         <v>2754000000</v>
       </c>
       <c r="K17" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>22.58</v>
       </c>
       <c r="L17" s="2">
         <v>7.29</v>
       </c>
       <c r="M17" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1387</v>
       </c>
       <c r="N17" s="10">
@@ -10706,8 +11170,11 @@
       <c r="Q17" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:17">
+      <c r="R17" s="14">
+        <v>7208.45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
       <c r="A18" s="2">
         <v>2020.5</v>
       </c>
@@ -10718,7 +11185,7 @@
         <v>1304000000</v>
       </c>
       <c r="D18" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4.29</v>
       </c>
       <c r="E18" s="4">
@@ -10728,7 +11195,7 @@
         <v>830000000</v>
       </c>
       <c r="G18" s="2">
-        <f>ROUND(F18/B18*100,2)</f>
+        <f t="shared" si="1"/>
         <v>2.73</v>
       </c>
       <c r="H18" s="2">
@@ -10741,14 +11208,14 @@
         <v>1554000000</v>
       </c>
       <c r="K18" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>11.65</v>
       </c>
       <c r="L18" s="2">
         <v>11.22</v>
       </c>
       <c r="M18" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>436</v>
       </c>
       <c r="N18" s="10">
@@ -10763,8 +11230,11 @@
       <c r="Q18" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:17">
+      <c r="R18" s="14">
+        <v>6432.04</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
       <c r="A19" s="2">
         <v>2021.5</v>
       </c>
@@ -10775,7 +11245,7 @@
         <v>721000000</v>
       </c>
       <c r="D19" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.2200000000000002</v>
       </c>
       <c r="E19" s="4">
@@ -10785,7 +11255,7 @@
         <v>245000000</v>
       </c>
       <c r="G19" s="2">
-        <f>ROUND(F19/B19*100,2)</f>
+        <f t="shared" si="1"/>
         <v>0.75</v>
       </c>
       <c r="H19" s="2">
@@ -10798,14 +11268,14 @@
         <v>1584000000</v>
       </c>
       <c r="K19" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>13.14</v>
       </c>
       <c r="L19" s="2">
         <v>3.85</v>
       </c>
       <c r="M19" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1318</v>
       </c>
       <c r="N19" s="10">
@@ -10820,8 +11290,11 @@
       <c r="Q19" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:17">
+      <c r="R19" s="14">
+        <v>6839.65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
       <c r="A20" s="2">
         <v>2022.5</v>
       </c>
@@ -10832,7 +11305,7 @@
         <v>1482000000</v>
       </c>
       <c r="D20" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4.34</v>
       </c>
       <c r="E20" s="4">
@@ -10842,7 +11315,7 @@
         <v>929000000</v>
       </c>
       <c r="G20" s="2">
-        <f>ROUND(F20/B20*100,2)</f>
+        <f t="shared" si="1"/>
         <v>2.72</v>
       </c>
       <c r="H20" s="2">
@@ -10855,14 +11328,14 @@
         <v>1849000000</v>
       </c>
       <c r="K20" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>13.53</v>
       </c>
       <c r="L20" s="2">
         <v>3.85</v>
       </c>
       <c r="M20" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>747</v>
       </c>
       <c r="N20" s="10">
@@ -10877,8 +11350,11 @@
       <c r="Q20" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:17">
+      <c r="R20" s="14">
+        <v>7434.27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
       <c r="A21" s="2">
         <v>2023.5</v>
       </c>
@@ -10889,7 +11365,7 @@
         <v>1426000000</v>
       </c>
       <c r="D21" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4.22</v>
       </c>
       <c r="E21" s="4">
@@ -10899,7 +11375,7 @@
         <v>929000000</v>
       </c>
       <c r="G21" s="2">
-        <f>ROUND(F21/B21*100,2)</f>
+        <f t="shared" si="1"/>
         <v>2.75</v>
       </c>
       <c r="H21" s="2">
@@ -10912,14 +11388,14 @@
         <v>1849000000</v>
       </c>
       <c r="K21" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>15.34</v>
       </c>
       <c r="L21" s="2">
         <v>12.1</v>
       </c>
       <c r="M21" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>747</v>
       </c>
       <c r="N21" s="10">
@@ -10934,8 +11410,11 @@
       <c r="Q21" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:17">
+      <c r="R21" s="14">
+        <v>7725.17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
       <c r="A22" s="2">
         <v>2024.5</v>
       </c>
@@ -10946,7 +11425,7 @@
         <v>1612000000</v>
       </c>
       <c r="D22" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4.6399999999999997</v>
       </c>
       <c r="E22" s="4">
@@ -10956,7 +11435,7 @@
         <v>1051000000</v>
       </c>
       <c r="G22" s="2">
-        <f>ROUND(F22/B22*100,2)</f>
+        <f t="shared" si="1"/>
         <v>3.02</v>
       </c>
       <c r="H22" s="2">
@@ -10969,14 +11448,14 @@
         <v>2337000000</v>
       </c>
       <c r="K22" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>20.18</v>
       </c>
       <c r="L22" s="2">
         <v>13.7</v>
       </c>
       <c r="M22" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2542</v>
       </c>
       <c r="N22" s="10">
@@ -10990,6 +11469,9 @@
       </c>
       <c r="Q22" s="2">
         <v>0</v>
+      </c>
+      <c r="R22" s="14">
+        <v>7918.4</v>
       </c>
     </row>
   </sheetData>
@@ -10999,7 +11481,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Q64"/>
+  <dimension ref="A1:R64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
@@ -11017,9 +11499,10 @@
     <col min="14" max="14" width="16.7109375" customWidth="1"/>
     <col min="15" max="15" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11068,11 +11551,14 @@
       <c r="P1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="14" t="s">
+      <c r="Q1" s="5" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:17">
+      <c r="R1" s="13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2" s="2">
         <v>2015</v>
       </c>
@@ -11128,8 +11614,11 @@
       <c r="Q2" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:17">
+      <c r="R2" s="2">
+        <v>6641.77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3" s="2">
         <v>2016</v>
       </c>
@@ -11185,8 +11674,11 @@
       <c r="Q3" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:17">
+      <c r="R3" s="2">
+        <v>6335.38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" s="2">
         <v>2017</v>
       </c>
@@ -11242,8 +11734,11 @@
       <c r="Q4" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:17">
+      <c r="R4" s="2">
+        <v>6842.83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5" s="2">
         <v>2018</v>
       </c>
@@ -11299,8 +11794,11 @@
       <c r="Q5" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:17">
+      <c r="R5" s="2">
+        <v>7428.21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6" s="2">
         <v>2019</v>
       </c>
@@ -11356,8 +11854,11 @@
       <c r="Q6" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:17">
+      <c r="R6" s="14">
+        <v>7276.89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
       <c r="A7" s="2">
         <v>2020</v>
       </c>
@@ -11413,8 +11914,11 @@
       <c r="Q7" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:17">
+      <c r="R7" s="14">
+        <v>7341.89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
       <c r="A8" s="2">
         <v>2021</v>
       </c>
@@ -11470,8 +11974,11 @@
       <c r="Q8" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:17">
+      <c r="R8" s="14">
+        <v>6122.66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
       <c r="A9" s="2">
         <v>2022</v>
       </c>
@@ -11527,8 +12034,11 @@
       <c r="Q9" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:17">
+      <c r="R9" s="14">
+        <v>7159.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
       <c r="A10" s="2">
         <v>2023</v>
       </c>
@@ -11584,8 +12094,11 @@
       <c r="Q10" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:17">
+      <c r="R10" s="14">
+        <v>7283.02</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
       <c r="A11" s="2">
         <v>2024</v>
       </c>
@@ -11641,8 +12154,11 @@
       <c r="Q11" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:17">
+      <c r="R11" s="14">
+        <v>7508.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
       <c r="A12" s="2">
         <v>2025</v>
       </c>
@@ -11698,8 +12214,11 @@
       <c r="Q12" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:17">
+      <c r="R12" s="14">
+        <v>8231.6200000000008</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
       <c r="A13" s="2">
         <v>2015.5</v>
       </c>
@@ -11755,8 +12274,11 @@
       <c r="Q13" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:17">
+      <c r="R13" s="14">
+        <v>6855.45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
       <c r="A14" s="2">
         <v>2016.5</v>
       </c>
@@ -11812,8 +12334,11 @@
       <c r="Q14" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17">
+      <c r="R14" s="14">
+        <v>6097.14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
       <c r="A15" s="2">
         <v>2017.5</v>
       </c>
@@ -11869,8 +12394,11 @@
       <c r="Q15" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17">
+      <c r="R15" s="14">
+        <v>7330.76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
       <c r="A16" s="2">
         <v>2018.5</v>
       </c>
@@ -11926,8 +12454,11 @@
       <c r="Q16" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:17">
+      <c r="R16" s="14">
+        <v>7450.95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
       <c r="A17" s="2">
         <v>2019.5</v>
       </c>
@@ -11983,8 +12514,11 @@
       <c r="Q17" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:17">
+      <c r="R17" s="14">
+        <v>7208.45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
       <c r="A18" s="2">
         <v>2020.5</v>
       </c>
@@ -12040,8 +12574,11 @@
       <c r="Q18" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:17">
+      <c r="R18" s="14">
+        <v>6432.04</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
       <c r="A19" s="2">
         <v>2021.5</v>
       </c>
@@ -12097,8 +12634,11 @@
       <c r="Q19" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:17">
+      <c r="R19" s="14">
+        <v>6839.65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
       <c r="A20" s="2">
         <v>2022.5</v>
       </c>
@@ -12154,8 +12694,11 @@
       <c r="Q20" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:17">
+      <c r="R20" s="14">
+        <v>7434.27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
       <c r="A21" s="2">
         <v>2023.5</v>
       </c>
@@ -12211,8 +12754,11 @@
       <c r="Q21" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:17">
+      <c r="R21" s="14">
+        <v>7725.17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
       <c r="A22" s="2">
         <v>2024.5</v>
       </c>
@@ -12267,6 +12813,9 @@
       </c>
       <c r="Q22" s="2">
         <v>0</v>
+      </c>
+      <c r="R22" s="14">
+        <v>7918.4</v>
       </c>
     </row>
     <row r="34" spans="1:11">
